--- a/results/research_results.xlsx
+++ b/results/research_results.xlsx
@@ -2,18 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf09909faad684ca6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_All_Data" sheetId="2" r:id="R5505ad568cfb45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Group_Comparison" sheetId="3" r:id="Rd51e1666f7c34308"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Region_Means" sheetId="4" r:id="Re7b4e7aaeed443b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Yearly_Means" sheetId="5" r:id="Rada2cca0ce2c4df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Exposed_Data" sheetId="6" r:id="R7813a47329524529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_PCA_Diagnostics" sheetId="7" r:id="R139a893c3f2147af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_PCA_Coefficients" sheetId="8" r:id="Rce872dee787a4610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_PCA_Scores" sheetId="9" r:id="R25925a2afcba4359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Model_Comparison" sheetId="10" r:id="Rac637146cb344175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_OLS_Coefficients" sheetId="11" r:id="Rd40e348ba29c4747"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Fitted_Mortality" sheetId="12" r:id="R590ac771b38c4c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R8034cc70f9044f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_All_Data" sheetId="2" r:id="R08457d109bcb480a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Group_Comparison" sheetId="3" r:id="R5f085f419d7c4cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Region_Means" sheetId="4" r:id="Rf3502e8f668a40c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Yearly_Means" sheetId="5" r:id="Rb94c181073b54d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Exposed_Data" sheetId="6" r:id="R4aacfe85c7094631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_PCA_Diagnostics" sheetId="7" r:id="R5cf3fe1d93824b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_PCA_Coefficients" sheetId="8" r:id="R12c3802a6b4f4020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_PCA_Scores" sheetId="9" r:id="R46fa271f8c9f4bcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Model_Comparison" sheetId="10" r:id="Rbf1916d93a8149eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_OLS_Coefficients" sheetId="11" r:id="R55d3151802484d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Fitted_Mortality" sheetId="12" r:id="R45845ced5a6c422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Boundary_Sensitivity" sheetId="13" r:id="Rb4d2653ac18b4bdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Pre2022_Group_Comparison" sheetId="14" r:id="R92ae111f6cd34c25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ1_Pre2022_Region_Means" sheetId="15" r:id="Rab1254ae407c4b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Boundary_Comparison" sheetId="16" r:id="R58e4da088c46467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Pre2022_Model_Comparison" sheetId="17" r:id="Raab946f3882e40d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Pre2022_Diagnostics" sheetId="18" r:id="Rd8c418897b5e48f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Pre2022_PCA_Coefficients" sheetId="19" r:id="R22bea8f7d3b547bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Pre2022_PCA_Scores" sheetId="20" r:id="R186fa3fea2d149f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Pre2022_OLS_Coefficients" sheetId="21" r:id="R97012fb9fa814409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ2_Pre2022_Fitted_Mortality" sheetId="22" r:id="Rde9e1e38d17f4a29"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,9 +34,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0.0000"/>
     <x:numFmt numFmtId="201" formatCode="0.00%"/>
+    <x:numFmt numFmtId="202" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -51,12 +62,27 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -81,7 +107,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="61">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -180,6 +206,33 @@
     <x:xf numFmtId="200" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -382,230 +435,440 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="45" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="58" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="str">
+      <x:c r="A1" s="54" t="str">
         <x:v>Kazakhstan Regional Health PCA Research - Repository Results</x:v>
       </x:c>
-      <x:c r="B1" s="25"/>
-      <x:c r="C1" s="25"/>
-      <x:c r="D1" s="25"/>
-      <x:c r="E1" s="25"/>
-      <x:c r="F1" s="25"/>
+      <x:c r="B1" s="54"/>
+      <x:c r="C1" s="54"/>
+      <x:c r="D1" s="54"/>
+      <x:c r="E1" s="54"/>
+      <x:c r="F1" s="54"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="25"/>
-      <x:c r="B2" s="25"/>
-      <x:c r="C2" s="25"/>
-      <x:c r="D2" s="25"/>
-      <x:c r="E2" s="25"/>
-      <x:c r="F2" s="25"/>
+      <x:c r="A2" s="52"/>
+      <x:c r="B2" s="52"/>
+      <x:c r="C2" s="52"/>
+      <x:c r="D2" s="52"/>
+      <x:c r="E2" s="52"/>
+      <x:c r="F2" s="52"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="26" t="str">
+      <x:c r="A3" s="57" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B3" s="26" t="str">
+      <x:c r="B3" s="57" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C3" s="25"/>
-      <x:c r="D3" s="25"/>
-      <x:c r="E3" s="25"/>
-      <x:c r="F3" s="25"/>
+      <x:c r="C3" s="52"/>
+      <x:c r="D3" s="52"/>
+      <x:c r="E3" s="52"/>
+      <x:c r="F3" s="52"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="25" t="str">
+      <x:c r="A4" s="52" t="str">
         <x:v>RQ1</x:v>
       </x:c>
-      <x:c r="B4" s="25" t="str">
+      <x:c r="B4" s="52" t="str">
         <x:v>6 regions, exposed-classified vs comparison-classified</x:v>
       </x:c>
-      <x:c r="C4" s="25"/>
-      <x:c r="D4" s="25"/>
-      <x:c r="E4" s="25"/>
-      <x:c r="F4" s="25"/>
+      <x:c r="C4" s="52"/>
+      <x:c r="D4" s="52"/>
+      <x:c r="E4" s="52"/>
+      <x:c r="F4" s="52"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="25" t="str">
+      <x:c r="A5" s="52" t="str">
         <x:v>RQ2</x:v>
       </x:c>
-      <x:c r="B5" s="25" t="str">
+      <x:c r="B5" s="52" t="str">
         <x:v>3 exposed-classified regions only</x:v>
       </x:c>
-      <x:c r="C5" s="25"/>
-      <x:c r="D5" s="25"/>
-      <x:c r="E5" s="25"/>
-      <x:c r="F5" s="25"/>
+      <x:c r="C5" s="52"/>
+      <x:c r="D5" s="52"/>
+      <x:c r="E5" s="52"/>
+      <x:c r="F5" s="52"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="25" t="str">
+      <x:c r="A6" s="52" t="str">
         <x:v>Study years</x:v>
       </x:c>
-      <x:c r="B6" s="25" t="str">
+      <x:c r="B6" s="52" t="str">
         <x:v>2011-2024</x:v>
       </x:c>
-      <x:c r="C6" s="25"/>
-      <x:c r="D6" s="25"/>
-      <x:c r="E6" s="25"/>
-      <x:c r="F6" s="25"/>
+      <x:c r="C6" s="52"/>
+      <x:c r="D6" s="52"/>
+      <x:c r="E6" s="52"/>
+      <x:c r="F6" s="52"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="25" t="str">
+      <x:c r="A7" s="52" t="str">
         <x:v>RQ2 rows</x:v>
       </x:c>
-      <x:c r="B7" s="25" t="n">
+      <x:c r="B7" s="58" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C7" s="25"/>
-      <x:c r="D7" s="25"/>
-      <x:c r="E7" s="25"/>
-      <x:c r="F7" s="25"/>
+      <x:c r="C7" s="52"/>
+      <x:c r="D7" s="52"/>
+      <x:c r="E7" s="52"/>
+      <x:c r="F7" s="52"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="25" t="str">
+      <x:c r="A8" s="52" t="str">
         <x:v>RQ2 Overall KMO</x:v>
       </x:c>
-      <x:c r="B8" s="27" t="n">
-        <x:v>0.5098916314</x:v>
-      </x:c>
-      <x:c r="C8" s="25"/>
-      <x:c r="D8" s="25"/>
-      <x:c r="E8" s="25"/>
-      <x:c r="F8" s="25"/>
+      <x:c r="B8" s="16" t="n">
+        <x:v>0.5098916313759189</x:v>
+      </x:c>
+      <x:c r="C8" s="52"/>
+      <x:c r="D8" s="52"/>
+      <x:c r="E8" s="52"/>
+      <x:c r="F8" s="52"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="25" t="str">
+      <x:c r="A9" s="52" t="str">
         <x:v>RQ2 PC1+PC2 variance</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="n">
-        <x:v>0.7521117789</x:v>
-      </x:c>
-      <x:c r="C9" s="25"/>
-      <x:c r="D9" s="25"/>
-      <x:c r="E9" s="25"/>
-      <x:c r="F9" s="25"/>
+      <x:c r="B9" s="18" t="n">
+        <x:v>0.7521117789049503</x:v>
+      </x:c>
+      <x:c r="C9" s="52"/>
+      <x:c r="D9" s="52"/>
+      <x:c r="E9" s="52"/>
+      <x:c r="F9" s="52"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="25" t="str">
-        <x:v>Before PCA R²</x:v>
-      </x:c>
-      <x:c r="B10" s="27" t="n">
-        <x:v>0.311240605</x:v>
-      </x:c>
-      <x:c r="C10" s="25"/>
-      <x:c r="D10" s="25"/>
-      <x:c r="E10" s="25"/>
-      <x:c r="F10" s="25"/>
+      <x:c r="A10" s="52" t="str">
+        <x:v>Baseline R²</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="n">
+        <x:v>0.08395152419528318</x:v>
+      </x:c>
+      <x:c r="C10" s="52"/>
+      <x:c r="D10" s="52"/>
+      <x:c r="E10" s="52"/>
+      <x:c r="F10" s="52"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="25" t="str">
-        <x:v>After PCA R²</x:v>
-      </x:c>
-      <x:c r="B11" s="25" t="n">
-        <x:v>0.2639262881</x:v>
-      </x:c>
-      <x:c r="C11" s="25"/>
-      <x:c r="D11" s="25"/>
-      <x:c r="E11" s="25"/>
-      <x:c r="F11" s="25"/>
+      <x:c r="A11" s="52" t="str">
+        <x:v>Baseline RMSE</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="n">
+        <x:v>0.10233318411823028</x:v>
+      </x:c>
+      <x:c r="C11" s="52"/>
+      <x:c r="D11" s="52"/>
+      <x:c r="E11" s="52"/>
+      <x:c r="F11" s="52"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="25" t="str">
-        <x:v>Before PCA RMSE</x:v>
-      </x:c>
-      <x:c r="B12" s="25" t="n">
-        <x:v>0.0887341978</x:v>
-      </x:c>
-      <x:c r="C12" s="25"/>
-      <x:c r="D12" s="25"/>
-      <x:c r="E12" s="25"/>
-      <x:c r="F12" s="25"/>
+      <x:c r="A12" s="52" t="str">
+        <x:v>Baseline AIC</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="n">
+        <x:v>-64.28895057894854</x:v>
+      </x:c>
+      <x:c r="C12" s="52"/>
+      <x:c r="D12" s="52"/>
+      <x:c r="E12" s="52"/>
+      <x:c r="F12" s="52"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="25"/>
-      <x:c r="B13" s="25"/>
-      <x:c r="C13" s="25"/>
-      <x:c r="D13" s="25"/>
-      <x:c r="E13" s="25"/>
-      <x:c r="F13" s="25"/>
+      <x:c r="A13" s="52" t="str">
+        <x:v>Original-indicator R²</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="n">
+        <x:v>0.3112406050470612</x:v>
+      </x:c>
+      <x:c r="C13" s="52"/>
+      <x:c r="D13" s="52"/>
+      <x:c r="E13" s="52"/>
+      <x:c r="F13" s="52"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="29" t="str">
+      <x:c r="A14" s="52" t="str">
+        <x:v>Original-indicator RMSE</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="n">
+        <x:v>0.08873419775528259</x:v>
+      </x:c>
+      <x:c r="C14" s="52"/>
+      <x:c r="D14" s="52"/>
+      <x:c r="E14" s="52"/>
+      <x:c r="F14" s="52"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="52" t="str">
+        <x:v>Original-indicator AIC</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="n">
+        <x:v>-66.26639648590324</x:v>
+      </x:c>
+      <x:c r="C15" s="52"/>
+      <x:c r="D15" s="52"/>
+      <x:c r="E15" s="52"/>
+      <x:c r="F15" s="52"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="52" t="str">
+        <x:v>PCA-reduced R²</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="n">
+        <x:v>0.26392628806790863</x:v>
+      </x:c>
+      <x:c r="C16" s="52"/>
+      <x:c r="D16" s="52"/>
+      <x:c r="E16" s="52"/>
+      <x:c r="F16" s="52"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="52" t="str">
+        <x:v>PCA-reduced RMSE</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="n">
+        <x:v>0.09173137705533681</x:v>
+      </x:c>
+      <x:c r="C17" s="52"/>
+      <x:c r="D17" s="52"/>
+      <x:c r="E17" s="52"/>
+      <x:c r="F17" s="52"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="52" t="str">
+        <x:v>PCA-reduced AIC</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="n">
+        <x:v>-69.47598936276958</x:v>
+      </x:c>
+      <x:c r="C18" s="52"/>
+      <x:c r="D18" s="52"/>
+      <x:c r="E18" s="52"/>
+      <x:c r="F18" s="52"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="52" t="str">
+        <x:v>RQ1 primary test</x:v>
+      </x:c>
+      <x:c r="B19" s="52" t="str">
+        <x:v>Exact permutation of six regional means (20 allocations)</x:v>
+      </x:c>
+      <x:c r="C19" s="52"/>
+      <x:c r="D19" s="52"/>
+      <x:c r="E19" s="52"/>
+      <x:c r="F19" s="52"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="52" t="str">
+        <x:v>Boundary sensitivity</x:v>
+      </x:c>
+      <x:c r="B20" s="52" t="str">
+        <x:v>2011-2021, RQ1 and RQ2</x:v>
+      </x:c>
+      <x:c r="C20" s="52"/>
+      <x:c r="D20" s="52"/>
+      <x:c r="E20" s="52"/>
+      <x:c r="F20" s="52"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="52" t="str">
+        <x:v>Pre-2022 RQ2 rows</x:v>
+      </x:c>
+      <x:c r="B21" s="58" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C21" s="52"/>
+      <x:c r="D21" s="52"/>
+      <x:c r="E21" s="52"/>
+      <x:c r="F21" s="52"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="52" t="str">
+        <x:v>Pre-2022 Overall KMO</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="n">
+        <x:v>0.4932114401561532</x:v>
+      </x:c>
+      <x:c r="C22" s="52"/>
+      <x:c r="D22" s="52"/>
+      <x:c r="E22" s="52"/>
+      <x:c r="F22" s="52"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="52"/>
+      <x:c r="B23" s="52"/>
+      <x:c r="C23" s="52"/>
+      <x:c r="D23" s="52"/>
+      <x:c r="E23" s="52"/>
+      <x:c r="F23" s="52"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="60" t="str">
         <x:v>Important interpretation note</x:v>
       </x:c>
-      <x:c r="B14" s="25"/>
-      <x:c r="C14" s="25"/>
-      <x:c r="D14" s="25"/>
-      <x:c r="E14" s="25"/>
-      <x:c r="F14" s="25"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="25" t="str">
+      <x:c r="B24" s="60"/>
+      <x:c r="C24" s="60"/>
+      <x:c r="D24" s="60"/>
+      <x:c r="E24" s="60"/>
+      <x:c r="F24" s="60"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="52" t="str">
         <x:v>Observed mortality is calculated from registered deaths / population × 100.</x:v>
       </x:c>
-      <x:c r="B15" s="25"/>
-      <x:c r="C15" s="25"/>
-      <x:c r="D15" s="25"/>
-      <x:c r="E15" s="25"/>
-      <x:c r="F15" s="25"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="25" t="str">
+      <x:c r="B25" s="52"/>
+      <x:c r="C25" s="52"/>
+      <x:c r="D25" s="52"/>
+      <x:c r="E25" s="52"/>
+      <x:c r="F25" s="52"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="52" t="str">
         <x:v>Mortality is NOT included in PCA.</x:v>
       </x:c>
-      <x:c r="B16" s="25"/>
-      <x:c r="C16" s="25"/>
-      <x:c r="D16" s="25"/>
-      <x:c r="E16" s="25"/>
-      <x:c r="F16" s="25"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="25" t="str">
+      <x:c r="B26" s="52"/>
+      <x:c r="C26" s="52"/>
+      <x:c r="D26" s="52"/>
+      <x:c r="E26" s="52"/>
+      <x:c r="F26" s="52"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="52" t="str">
         <x:v>HC3 changes SE/p-values, not fitted mortality values.</x:v>
       </x:c>
-      <x:c r="B17" s="25"/>
-      <x:c r="C17" s="25"/>
-      <x:c r="D17" s="25"/>
-      <x:c r="E17" s="25"/>
-      <x:c r="F17" s="25"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="25" t="str">
+      <x:c r="B27" s="52"/>
+      <x:c r="C27" s="52"/>
+      <x:c r="D27" s="52"/>
+      <x:c r="E27" s="52"/>
+      <x:c r="F27" s="52"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="52" t="str">
         <x:v>All RQ2 model metrics are in-sample.</x:v>
       </x:c>
-      <x:c r="B18" s="25"/>
-      <x:c r="C18" s="25"/>
-      <x:c r="D18" s="25"/>
-      <x:c r="E18" s="25"/>
-      <x:c r="F18" s="25"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="25"/>
-      <x:c r="B19" s="25"/>
-      <x:c r="C19" s="25"/>
-      <x:c r="D19" s="25"/>
-      <x:c r="E19" s="25"/>
-      <x:c r="F19" s="25"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="25"/>
-      <x:c r="B20" s="25"/>
-      <x:c r="C20" s="25"/>
-      <x:c r="D20" s="25"/>
-      <x:c r="E20" s="25"/>
-      <x:c r="F20" s="25"/>
+      <x:c r="B28" s="52"/>
+      <x:c r="C28" s="52"/>
+      <x:c r="D28" s="52"/>
+      <x:c r="E28" s="52"/>
+      <x:c r="F28" s="52"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="52" t="str">
+        <x:v>Welch results are secondary. RQ1 uses exact region-label permutation tests.</x:v>
+      </x:c>
+      <x:c r="B29" s="52"/>
+      <x:c r="C29" s="52"/>
+      <x:c r="D29" s="52"/>
+      <x:c r="E29" s="52"/>
+      <x:c r="F29" s="52"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="52" t="str">
+        <x:v>Pre-2022 analysis refits standardization, PCA and all three OLS models.</x:v>
+      </x:c>
+      <x:c r="B30" s="52"/>
+      <x:c r="C30" s="52"/>
+      <x:c r="D30" s="52"/>
+      <x:c r="E30" s="52"/>
+      <x:c r="F30" s="52"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="52"/>
+      <x:c r="B31" s="52"/>
+      <x:c r="C31" s="52"/>
+      <x:c r="D31" s="52"/>
+      <x:c r="E31" s="52"/>
+      <x:c r="F31" s="52"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="52"/>
+      <x:c r="B32" s="52"/>
+      <x:c r="C32" s="52"/>
+      <x:c r="D32" s="52"/>
+      <x:c r="E32" s="52"/>
+      <x:c r="F32" s="52"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="52"/>
+      <x:c r="B33" s="52"/>
+      <x:c r="C33" s="52"/>
+      <x:c r="D33" s="52"/>
+      <x:c r="E33" s="52"/>
+      <x:c r="F33" s="52"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="52"/>
+      <x:c r="B34" s="52"/>
+      <x:c r="C34" s="52"/>
+      <x:c r="D34" s="52"/>
+      <x:c r="E34" s="52"/>
+      <x:c r="F34" s="52"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="52"/>
+      <x:c r="B35" s="52"/>
+      <x:c r="C35" s="52"/>
+      <x:c r="D35" s="52"/>
+      <x:c r="E35" s="52"/>
+      <x:c r="F35" s="52"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="52"/>
+      <x:c r="B36" s="52"/>
+      <x:c r="C36" s="52"/>
+      <x:c r="D36" s="52"/>
+      <x:c r="E36" s="52"/>
+      <x:c r="F36" s="52"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="52"/>
+      <x:c r="B37" s="52"/>
+      <x:c r="C37" s="52"/>
+      <x:c r="D37" s="52"/>
+      <x:c r="E37" s="52"/>
+      <x:c r="F37" s="52"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="52"/>
+      <x:c r="B38" s="52"/>
+      <x:c r="C38" s="52"/>
+      <x:c r="D38" s="52"/>
+      <x:c r="E38" s="52"/>
+      <x:c r="F38" s="52"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="52"/>
+      <x:c r="B39" s="52"/>
+      <x:c r="C39" s="52"/>
+      <x:c r="D39" s="52"/>
+      <x:c r="E39" s="52"/>
+      <x:c r="F39" s="52"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="52"/>
+      <x:c r="B40" s="52"/>
+      <x:c r="C40" s="52"/>
+      <x:c r="D40" s="52"/>
+      <x:c r="E40" s="52"/>
+      <x:c r="F40" s="52"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A14:F14"/>
-    <x:mergeCell ref="A15:F15"/>
-    <x:mergeCell ref="A16:F16"/>
-    <x:mergeCell ref="A17:F17"/>
-    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A24:F24"/>
+    <x:mergeCell ref="A25:F25"/>
+    <x:mergeCell ref="A26:F26"/>
+    <x:mergeCell ref="A27:F27"/>
+    <x:mergeCell ref="A28:F28"/>
+    <x:mergeCell ref="A29:F29"/>
+    <x:mergeCell ref="A30:F30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -615,7 +878,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
@@ -625,82 +888,108 @@
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="39" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="46" t="str">
         <x:v>Model</x:v>
       </x:c>
-      <x:c r="B1" s="39" t="str">
+      <x:c r="B1" s="46" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="C1" s="39" t="str">
+      <x:c r="C1" s="46" t="str">
         <x:v>Parameters</x:v>
       </x:c>
-      <x:c r="D1" s="44" t="str">
+      <x:c r="D1" s="47" t="str">
         <x:v>R2</x:v>
       </x:c>
-      <x:c r="E1" s="44" t="str">
+      <x:c r="E1" s="47" t="str">
         <x:v>Adjusted_R2</x:v>
       </x:c>
-      <x:c r="F1" s="44" t="str">
+      <x:c r="F1" s="47" t="str">
         <x:v>RMSE</x:v>
       </x:c>
-      <x:c r="G1" s="44" t="str">
+      <x:c r="G1" s="47" t="str">
         <x:v>AIC</x:v>
       </x:c>
-      <x:c r="H1" s="44" t="str">
+      <x:c r="H1" s="47" t="str">
         <x:v>BIC</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="25" t="str">
-        <x:v>Before PCA - 5 original indicators</x:v>
+        <x:v>Baseline - Region + Year</x:v>
       </x:c>
       <x:c r="B2" s="25" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C2" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="25" t="n">
-        <x:v>0.3112406050470613</x:v>
+        <x:v>0.08395152419528318</x:v>
       </x:c>
       <x:c r="E2" s="25" t="n">
-        <x:v>0.14426863051301553</x:v>
+        <x:v>0.01163190768438449</x:v>
       </x:c>
       <x:c r="F2" s="25" t="n">
-        <x:v>0.08873419775528257</x:v>
+        <x:v>0.10233318411823028</x:v>
       </x:c>
       <x:c r="G2" s="25" t="n">
-        <x:v>-66.26639648590324</x:v>
+        <x:v>-64.28895057894854</x:v>
       </x:c>
       <x:c r="H2" s="25" t="n">
-        <x:v>-50.62736992135293</x:v>
+        <x:v>-57.33827210581507</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="25" t="str">
-        <x:v>After PCA - PC1 + PC2</x:v>
+        <x:v>Before PCA - 5 original indicators</x:v>
       </x:c>
       <x:c r="B3" s="25" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C3" s="25" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="25" t="n">
+        <x:v>0.3112406050470612</x:v>
+      </x:c>
+      <x:c r="E3" s="25" t="n">
+        <x:v>0.14426863051301542</x:v>
+      </x:c>
+      <x:c r="F3" s="25" t="n">
+        <x:v>0.08873419775528259</x:v>
+      </x:c>
+      <x:c r="G3" s="25" t="n">
+        <x:v>-66.26639648590324</x:v>
+      </x:c>
+      <x:c r="H3" s="25" t="n">
+        <x:v>-50.62736992135293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>After PCA - PC1 + PC2</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D3" s="25" t="n">
-        <x:v>0.2639262880679091</x:v>
-      </x:c>
-      <x:c r="E3" s="25" t="n">
-        <x:v>0.1616938280773409</x:v>
-      </x:c>
-      <x:c r="F3" s="25" t="n">
-        <x:v>0.09173137705533678</x:v>
-      </x:c>
-      <x:c r="G3" s="25" t="n">
-        <x:v>-69.47598936276961</x:v>
-      </x:c>
-      <x:c r="H3" s="25" t="n">
-        <x:v>-59.0499716530694</x:v>
+      <x:c r="D4" t="n">
+        <x:v>0.26392628806790863</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>0.16169382807734045</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>0.09173137705533681</x:v>
+      </x:c>
+      <x:c r="G4" t="n">
+        <x:v>-69.47598936276958</x:v>
+      </x:c>
+      <x:c r="H4" t="n">
+        <x:v>-59.04997165306937</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -712,8 +1001,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
@@ -722,134 +1011,134 @@
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="39" t="str">
+    <x:row r="1" ht="44" customHeight="1">
+      <x:c r="A1" s="46" t="str">
         <x:v>Model</x:v>
       </x:c>
-      <x:c r="B1" s="44" t="str">
+      <x:c r="B1" s="47" t="str">
         <x:v>Term</x:v>
       </x:c>
-      <x:c r="C1" s="44" t="str">
+      <x:c r="C1" s="47" t="str">
         <x:v>Coefficient</x:v>
       </x:c>
-      <x:c r="D1" s="44" t="str">
+      <x:c r="D1" s="47" t="str">
         <x:v>HC3_SE</x:v>
       </x:c>
-      <x:c r="E1" s="44" t="str">
+      <x:c r="E1" s="47" t="str">
         <x:v>t</x:v>
       </x:c>
-      <x:c r="F1" s="44" t="str">
+      <x:c r="F1" s="47" t="str">
         <x:v>p_value</x:v>
       </x:c>
-      <x:c r="G1" s="44" t="str">
+      <x:c r="G1" s="47" t="str">
         <x:v>CI95_low</x:v>
       </x:c>
-      <x:c r="H1" s="44" t="str">
+      <x:c r="H1" s="47" t="str">
         <x:v>CI95_high</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="25" t="str">
-        <x:v>Before PCA</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B2" s="25" t="str">
         <x:v>Intercept</x:v>
       </x:c>
       <x:c r="C2" s="25" t="n">
-        <x:v>1.5263521468405266</x:v>
+        <x:v>1.091389558902275</x:v>
       </x:c>
       <x:c r="D2" s="25" t="n">
-        <x:v>1.4653950634024777</x:v>
+        <x:v>0.029467283718084266</x:v>
       </x:c>
       <x:c r="E2" s="25" t="n">
-        <x:v>1.041597713108514</x:v>
+        <x:v>37.037331616435424</x:v>
       </x:c>
       <x:c r="F2" s="25" t="n">
-        <x:v>0.2975982293976962</x:v>
+        <x:v>2.8723079819129194e-300</x:v>
       </x:c>
       <x:c r="G2" s="25" t="n">
-        <x:v>-1.3457694005511187</x:v>
+        <x:v>1.0336347440926064</x:v>
       </x:c>
       <x:c r="H2" s="25" t="n">
-        <x:v>4.398473694232171</x:v>
+        <x:v>1.1491443737119438</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="25" t="str">
-        <x:v>Before PCA</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B3" s="25" t="str">
-        <x:v>Cancer_pct</x:v>
+        <x:v>Year_centered</x:v>
       </x:c>
       <x:c r="C3" s="25" t="n">
-        <x:v>-2.013268784142124</x:v>
+        <x:v>-0.0034419609656130487</x:v>
       </x:c>
       <x:c r="D3" s="25" t="n">
-        <x:v>1.1982305522752106</x:v>
+        <x:v>0.003961733546553438</x:v>
       </x:c>
       <x:c r="E3" s="25" t="n">
-        <x:v>-1.6802015107354022</x:v>
+        <x:v>-0.8688017316579576</x:v>
       </x:c>
       <x:c r="F3" s="25" t="n">
-        <x:v>0.0929181155201912</x:v>
+        <x:v>0.38495558580487754</x:v>
       </x:c>
       <x:c r="G3" s="25" t="n">
-        <x:v>-4.361757511777075</x:v>
+        <x:v>-0.011206816033201925</x:v>
       </x:c>
       <x:c r="H3" s="25" t="n">
-        <x:v>0.3352199434928269</x:v>
+        <x:v>0.004322894101975828</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="25" t="str">
-        <x:v>Before PCA</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="25" t="str">
-        <x:v>Infant_mortality_pct</x:v>
+        <x:v>Region_Karaganda</x:v>
       </x:c>
       <x:c r="C4" s="25" t="n">
-        <x:v>0.15841478447590596</x:v>
+        <x:v>-0.05701795320932149</x:v>
       </x:c>
       <x:c r="D4" s="25" t="n">
-        <x:v>0.08080688212519202</x:v>
+        <x:v>0.04037068313977695</x:v>
       </x:c>
       <x:c r="E4" s="25" t="n">
-        <x:v>1.9604120380548529</x:v>
+        <x:v>-1.4123603757683778</x:v>
       </x:c>
       <x:c r="F4" s="25" t="n">
-        <x:v>0.04994764995330621</x:v>
+        <x:v>0.15784387736632732</x:v>
       </x:c>
       <x:c r="G4" s="25" t="n">
-        <x:v>0.00003620580755614444</x:v>
+        <x:v>-0.1361430381945627</x:v>
       </x:c>
       <x:c r="H4" s="25" t="n">
-        <x:v>0.31679336314425577</x:v>
+        <x:v>0.022107131775919733</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
-        <x:v>Before PCA</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B5" s="25" t="str">
-        <x:v>Circulatory_pct</x:v>
+        <x:v>Region_Pavlodar</x:v>
       </x:c>
       <x:c r="C5" s="25" t="n">
-        <x:v>0.005831019238746626</x:v>
+        <x:v>-0.06035425228153288</x:v>
       </x:c>
       <x:c r="D5" s="25" t="n">
-        <x:v>0.14431075851678773</x:v>
+        <x:v>0.04423592726689343</x:v>
       </x:c>
       <x:c r="E5" s="25" t="n">
-        <x:v>0.04040599120036017</x:v>
+        <x:v>-1.3643718129246167</x:v>
       </x:c>
       <x:c r="F5" s="25" t="n">
-        <x:v>0.9677694538644686</x:v>
+        <x:v>0.17245057456583401</x:v>
       </x:c>
       <x:c r="G5" s="25" t="n">
-        <x:v>-0.2770128700358142</x:v>
+        <x:v>-0.14705507654737737</x:v>
       </x:c>
       <x:c r="H5" s="25" t="n">
-        <x:v>0.28867490851330746</x:v>
+        <x:v>0.026346571984311604</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -857,25 +1146,25 @@
         <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B6" s="25" t="str">
-        <x:v>Disability_pct</x:v>
+        <x:v>Intercept</x:v>
       </x:c>
       <x:c r="C6" s="25" t="n">
-        <x:v>-0.048530473508526406</x:v>
+        <x:v>1.5263521468405203</x:v>
       </x:c>
       <x:c r="D6" s="25" t="n">
-        <x:v>0.12389083852722328</x:v>
+        <x:v>1.4653950634024715</x:v>
       </x:c>
       <x:c r="E6" s="25" t="n">
-        <x:v>-0.39171963064776993</x:v>
+        <x:v>1.0415977131085141</x:v>
       </x:c>
       <x:c r="F6" s="25" t="n">
-        <x:v>0.6952653837450083</x:v>
+        <x:v>0.2975982293976962</x:v>
       </x:c>
       <x:c r="G6" s="25" t="n">
-        <x:v>-0.2913520550363514</x:v>
+        <x:v>-1.345769400551113</x:v>
       </x:c>
       <x:c r="H6" s="25" t="n">
-        <x:v>0.19429110801929858</x:v>
+        <x:v>4.398473694232154</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -883,25 +1172,25 @@
         <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B7" s="25" t="str">
-        <x:v>Unemployment_pct</x:v>
+        <x:v>Cancer_pct</x:v>
       </x:c>
       <x:c r="C7" s="25" t="n">
-        <x:v>0.03653108962250412</x:v>
+        <x:v>-2.013268784142115</x:v>
       </x:c>
       <x:c r="D7" s="25" t="n">
-        <x:v>0.14226883454121944</x:v>
+        <x:v>1.1982305522752537</x:v>
       </x:c>
       <x:c r="E7" s="25" t="n">
-        <x:v>0.25677506771112263</x:v>
+        <x:v>-1.680201510735334</x:v>
       </x:c>
       <x:c r="F7" s="25" t="n">
-        <x:v>0.7973524179812818</x:v>
+        <x:v>0.09291811552020444</x:v>
       </x:c>
       <x:c r="G7" s="25" t="n">
-        <x:v>-0.242310702200774</x:v>
+        <x:v>-4.36175751177715</x:v>
       </x:c>
       <x:c r="H7" s="25" t="n">
-        <x:v>0.31537288144578224</x:v>
+        <x:v>0.3352199434929206</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -909,25 +1198,25 @@
         <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B8" s="25" t="str">
-        <x:v>Year_centered</x:v>
+        <x:v>Infant_mortality_pct</x:v>
       </x:c>
       <x:c r="C8" s="25" t="n">
-        <x:v>0.01313347453694913</x:v>
+        <x:v>0.15841478447590557</x:v>
       </x:c>
       <x:c r="D8" s="25" t="n">
-        <x:v>0.015478942115095049</x:v>
+        <x:v>0.08080688212518983</x:v>
       </x:c>
       <x:c r="E8" s="25" t="n">
-        <x:v>0.8484736514481425</x:v>
+        <x:v>1.9604120380549013</x:v>
       </x:c>
       <x:c r="F8" s="25" t="n">
-        <x:v>0.3961742402980817</x:v>
+        <x:v>0.049947649953300546</x:v>
       </x:c>
       <x:c r="G8" s="25" t="n">
-        <x:v>-0.017204694527417415</x:v>
+        <x:v>0.00003620580756003022</x:v>
       </x:c>
       <x:c r="H8" s="25" t="n">
-        <x:v>0.043471643601315675</x:v>
+        <x:v>0.3167933631442511</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -935,25 +1224,25 @@
         <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B9" s="25" t="str">
-        <x:v>Region_Karaganda</x:v>
+        <x:v>Circulatory_pct</x:v>
       </x:c>
       <x:c r="C9" s="25" t="n">
-        <x:v>-0.019520917967054935</x:v>
+        <x:v>0.00583101923874664</x:v>
       </x:c>
       <x:c r="D9" s="25" t="n">
-        <x:v>0.15848558365431542</x:v>
+        <x:v>0.1443107585167861</x:v>
       </x:c>
       <x:c r="E9" s="25" t="n">
-        <x:v>-0.12317156877582915</x:v>
+        <x:v>0.04040599120036072</x:v>
       </x:c>
       <x:c r="F9" s="25" t="n">
-        <x:v>0.9019712389373421</x:v>
+        <x:v>0.9677694538644681</x:v>
       </x:c>
       <x:c r="G9" s="25" t="n">
-        <x:v>-0.33014695399832306</x:v>
+        <x:v>-0.277012870035811</x:v>
       </x:c>
       <x:c r="H9" s="25" t="n">
-        <x:v>0.29110511806421313</x:v>
+        <x:v>0.28867490851330424</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -961,129 +1250,129 @@
         <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B10" s="25" t="str">
-        <x:v>Region_Pavlodar</x:v>
+        <x:v>Disability_pct</x:v>
       </x:c>
       <x:c r="C10" s="25" t="n">
-        <x:v>-0.013398685370478114</x:v>
+        <x:v>-0.04853047350852738</x:v>
       </x:c>
       <x:c r="D10" s="25" t="n">
-        <x:v>0.13246201915868214</x:v>
+        <x:v>0.12389083852722792</x:v>
       </x:c>
       <x:c r="E10" s="25" t="n">
-        <x:v>-0.10115114849961054</x:v>
+        <x:v>-0.3917196306477631</x:v>
       </x:c>
       <x:c r="F10" s="25" t="n">
-        <x:v>0.9194304755887424</x:v>
+        <x:v>0.6952653837450133</x:v>
       </x:c>
       <x:c r="G10" s="25" t="n">
-        <x:v>-0.27301947224094975</x:v>
+        <x:v>-0.2913520550363614</x:v>
       </x:c>
       <x:c r="H10" s="25" t="n">
-        <x:v>0.24622210149999352</x:v>
+        <x:v>0.19429110801930669</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="25" t="str">
-        <x:v>After PCA</x:v>
+        <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B11" s="25" t="str">
-        <x:v>Intercept</x:v>
+        <x:v>Unemployment_pct</x:v>
       </x:c>
       <x:c r="C11" s="25" t="n">
-        <x:v>1.1021090050224431</x:v>
+        <x:v>0.03653108962250434</x:v>
       </x:c>
       <x:c r="D11" s="25" t="n">
-        <x:v>0.03454371920968536</x:v>
+        <x:v>0.1422688345412154</x:v>
       </x:c>
       <x:c r="E11" s="25" t="n">
-        <x:v>31.90475809314227</x:v>
+        <x:v>0.25677506771113146</x:v>
       </x:c>
       <x:c r="F11" s="25" t="n">
-        <x:v>2.293673632150025e-223</x:v>
+        <x:v>0.797352417981275</x:v>
       </x:c>
       <x:c r="G11" s="25" t="n">
-        <x:v>1.0344045594793954</x:v>
+        <x:v>-0.24231070220076584</x:v>
       </x:c>
       <x:c r="H11" s="25" t="n">
-        <x:v>1.169813450565491</x:v>
+        <x:v>0.3153728814457745</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="25" t="str">
-        <x:v>After PCA</x:v>
+        <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B12" s="25" t="str">
-        <x:v>PC1</x:v>
+        <x:v>Year_centered</x:v>
       </x:c>
       <x:c r="C12" s="25" t="n">
-        <x:v>0.06286072207819916</x:v>
+        <x:v>0.013133474536949082</x:v>
       </x:c>
       <x:c r="D12" s="25" t="n">
-        <x:v>0.021414035101433984</x:v>
+        <x:v>0.015478942115094624</x:v>
       </x:c>
       <x:c r="E12" s="25" t="n">
-        <x:v>2.935491689466303</x:v>
+        <x:v>0.8484736514481627</x:v>
       </x:c>
       <x:c r="F12" s="25" t="n">
-        <x:v>0.0033301953170762916</x:v>
+        <x:v>0.39617424029807036</x:v>
       </x:c>
       <x:c r="G12" s="25" t="n">
-        <x:v>0.02088998451571203</x:v>
+        <x:v>-0.01720469452741663</x:v>
       </x:c>
       <x:c r="H12" s="25" t="n">
-        <x:v>0.1048314596406863</x:v>
+        <x:v>0.043471643601314794</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="25" t="str">
-        <x:v>After PCA</x:v>
+        <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B13" s="25" t="str">
-        <x:v>PC2</x:v>
+        <x:v>Region_Karaganda</x:v>
       </x:c>
       <x:c r="C13" s="25" t="n">
-        <x:v>0.027005056677704156</x:v>
+        <x:v>-0.019520917967054505</x:v>
       </x:c>
       <x:c r="D13" s="25" t="n">
-        <x:v>0.05272318942631121</x:v>
+        <x:v>0.1584855836543163</x:v>
       </x:c>
       <x:c r="E13" s="25" t="n">
-        <x:v>0.5122045341253091</x:v>
+        <x:v>-0.12317156877582573</x:v>
       </x:c>
       <x:c r="F13" s="25" t="n">
-        <x:v>0.6085078701475723</x:v>
+        <x:v>0.9019712389373448</x:v>
       </x:c>
       <x:c r="G13" s="25" t="n">
-        <x:v>-0.07633049574794881</x:v>
+        <x:v>-0.3301469539983244</x:v>
       </x:c>
       <x:c r="H13" s="25" t="n">
-        <x:v>0.13034060910335712</x:v>
+        <x:v>0.29110511806421535</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="25" t="str">
-        <x:v>After PCA</x:v>
+        <x:v>Before PCA</x:v>
       </x:c>
       <x:c r="B14" s="25" t="str">
-        <x:v>Year_centered</x:v>
+        <x:v>Region_Pavlodar</x:v>
       </x:c>
       <x:c r="C14" s="25" t="n">
-        <x:v>0.01806079102772916</x:v>
+        <x:v>-0.01339868537047817</x:v>
       </x:c>
       <x:c r="D14" s="25" t="n">
-        <x:v>0.010223853859493577</x:v>
+        <x:v>0.13246201915868133</x:v>
       </x:c>
       <x:c r="E14" s="25" t="n">
-        <x:v>1.766534545186053</x:v>
+        <x:v>-0.10115114849961158</x:v>
       </x:c>
       <x:c r="F14" s="25" t="n">
-        <x:v>0.0773062112654296</x:v>
+        <x:v>0.9194304755887416</x:v>
       </x:c>
       <x:c r="G14" s="25" t="n">
-        <x:v>-0.0019775943200790805</x:v>
+        <x:v>-0.2730194722409482</x:v>
       </x:c>
       <x:c r="H14" s="25" t="n">
-        <x:v>0.0380991763755374</x:v>
+        <x:v>0.24622210149999185</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1091,25 +1380,25 @@
         <x:v>After PCA</x:v>
       </x:c>
       <x:c r="B15" s="25" t="str">
-        <x:v>Region_Karaganda</x:v>
+        <x:v>Intercept</x:v>
       </x:c>
       <x:c r="C15" s="25" t="n">
-        <x:v>-0.11254319105972126</x:v>
+        <x:v>1.1021090050224427</x:v>
       </x:c>
       <x:c r="D15" s="25" t="n">
-        <x:v>0.10646152568010757</x:v>
+        <x:v>0.03454371920968542</x:v>
       </x:c>
       <x:c r="E15" s="25" t="n">
-        <x:v>-1.0571254764644995</x:v>
+        <x:v>31.904758093142203</x:v>
       </x:c>
       <x:c r="F15" s="25" t="n">
-        <x:v>0.2904543255009333</x:v>
+        <x:v>2.2936736321548535e-223</x:v>
       </x:c>
       <x:c r="G15" s="25" t="n">
-        <x:v>-0.3212039471319182</x:v>
+        <x:v>1.034404559479395</x:v>
       </x:c>
       <x:c r="H15" s="25" t="n">
-        <x:v>0.09611756501247566</x:v>
+        <x:v>1.1698134505654905</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1117,25 +1406,129 @@
         <x:v>After PCA</x:v>
       </x:c>
       <x:c r="B16" s="25" t="str">
+        <x:v>PC1</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="n">
+        <x:v>0.06286072207819902</x:v>
+      </x:c>
+      <x:c r="D16" s="25" t="n">
+        <x:v>0.02141403510143395</x:v>
+      </x:c>
+      <x:c r="E16" s="25" t="n">
+        <x:v>2.9354916894663012</x:v>
+      </x:c>
+      <x:c r="F16" s="25" t="n">
+        <x:v>0.0033301953170763116</x:v>
+      </x:c>
+      <x:c r="G16" s="25" t="n">
+        <x:v>0.02088998451571196</x:v>
+      </x:c>
+      <x:c r="H16" s="25" t="n">
+        <x:v>0.10483145964068609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>PC2</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>0.02700505667770384</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>0.05272318942631122</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>0.512204534125303</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>0.6085078701475766</x:v>
+      </x:c>
+      <x:c r="G17" t="n">
+        <x:v>-0.07633049574794915</x:v>
+      </x:c>
+      <x:c r="H17" t="n">
+        <x:v>0.13034060910335682</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Year_centered</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>0.018060791027728833</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>0.01022385385949353</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>1.7665345451860293</x:v>
+      </x:c>
+      <x:c r="F18" t="n">
+        <x:v>0.07730621126543354</x:v>
+      </x:c>
+      <x:c r="G18" t="n">
+        <x:v>-0.0019775943200793164</x:v>
+      </x:c>
+      <x:c r="H18" t="n">
+        <x:v>0.03809917637553698</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Region_Karaganda</x:v>
+      </x:c>
+      <x:c r="C19" t="n">
+        <x:v>-0.11254319105972052</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>0.10646152568010737</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>-1.0571254764644944</x:v>
+      </x:c>
+      <x:c r="F19" t="n">
+        <x:v>0.29045432550093575</x:v>
+      </x:c>
+      <x:c r="G19" t="n">
+        <x:v>-0.321203947131917</x:v>
+      </x:c>
+      <x:c r="H19" t="n">
+        <x:v>0.09611756501247601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
         <x:v>Region_Pavlodar</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="n">
-        <x:v>-0.036987352791634204</x:v>
-      </x:c>
-      <x:c r="D16" s="25" t="n">
-        <x:v>0.04104929652966726</x:v>
-      </x:c>
-      <x:c r="E16" s="25" t="n">
-        <x:v>-0.9010471778707</x:v>
-      </x:c>
-      <x:c r="F16" s="25" t="n">
-        <x:v>0.3675632361477351</x:v>
-      </x:c>
-      <x:c r="G16" s="25" t="n">
-        <x:v>-0.11744249558048706</x:v>
-      </x:c>
-      <x:c r="H16" s="25" t="n">
-        <x:v>0.04346778999721865</x:v>
+      <x:c r="C20" t="n">
+        <x:v>-0.036987352791634565</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>0.04104929652966708</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>-0.9010471778707128</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>0.36756323614772834</x:v>
+      </x:c>
+      <x:c r="G20" t="n">
+        <x:v>-0.11744249558048707</x:v>
+      </x:c>
+      <x:c r="H20" t="n">
+        <x:v>0.04346778999721794</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1154,28 +1547,36 @@
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="39" t="str">
+    <x:row r="1" ht="44" customHeight="1">
+      <x:c r="A1" s="46" t="str">
         <x:v>Region</x:v>
       </x:c>
-      <x:c r="B1" s="44" t="str">
+      <x:c r="B1" s="47" t="str">
         <x:v>Year</x:v>
       </x:c>
-      <x:c r="C1" s="44" t="str">
+      <x:c r="C1" s="47" t="str">
         <x:v>Observed_Mortality</x:v>
       </x:c>
-      <x:c r="D1" s="44" t="str">
+      <x:c r="D1" s="47" t="str">
+        <x:v>Fitted_Baseline</x:v>
+      </x:c>
+      <x:c r="E1" s="47" t="str">
+        <x:v>Residual_Baseline</x:v>
+      </x:c>
+      <x:c r="F1" s="47" t="str">
         <x:v>Fitted_Before_PCA</x:v>
       </x:c>
-      <x:c r="E1" s="44" t="str">
+      <x:c r="G1" s="47" t="str">
         <x:v>Residual_Before_PCA</x:v>
       </x:c>
-      <x:c r="F1" s="44" t="str">
+      <x:c r="H1" s="46" t="str">
         <x:v>Fitted_After_PCA</x:v>
       </x:c>
-      <x:c r="G1" s="44" t="str">
+      <x:c r="I1" s="46" t="str">
         <x:v>Residual_After_PCA</x:v>
       </x:c>
     </x:row>
@@ -1190,16 +1591,22 @@
         <x:v>1.1927803741994365</x:v>
       </x:c>
       <x:c r="D2" s="25" t="n">
-        <x:v>1.1922677573284841</x:v>
+        <x:v>1.11376230517876</x:v>
       </x:c>
       <x:c r="E2" s="25" t="n">
-        <x:v>0.0005126168709523871</x:v>
+        <x:v>0.07901806902067654</x:v>
       </x:c>
       <x:c r="F2" s="25" t="n">
-        <x:v>1.175886429737277</x:v>
+        <x:v>1.1922677573284772</x:v>
       </x:c>
       <x:c r="G2" s="25" t="n">
-        <x:v>0.016893944462159416</x:v>
+        <x:v>0.0005126168709592704</x:v>
+      </x:c>
+      <x:c r="H2" t="n">
+        <x:v>1.1758864297372784</x:v>
+      </x:c>
+      <x:c r="I2" t="n">
+        <x:v>0.016893944462158084</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1213,16 +1620,22 @@
         <x:v>1.1673333046607317</x:v>
       </x:c>
       <x:c r="D3" s="25" t="n">
-        <x:v>1.1667401098310104</x:v>
+        <x:v>1.1103203442131468</x:v>
       </x:c>
       <x:c r="E3" s="25" t="n">
-        <x:v>0.0005931948297213108</x:v>
+        <x:v>0.05701296044758486</x:v>
       </x:c>
       <x:c r="F3" s="25" t="n">
-        <x:v>1.1717752714016036</x:v>
+        <x:v>1.1667401098310035</x:v>
       </x:c>
       <x:c r="G3" s="25" t="n">
-        <x:v>-0.004441966740871939</x:v>
+        <x:v>0.0005931948297281942</x:v>
+      </x:c>
+      <x:c r="H3" t="n">
+        <x:v>1.171775271401605</x:v>
+      </x:c>
+      <x:c r="I3" t="n">
+        <x:v>-0.004441966740873271</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1236,16 +1649,22 @@
         <x:v>1.0989420889081452</x:v>
       </x:c>
       <x:c r="D4" s="25" t="n">
-        <x:v>1.109085881741928</x:v>
+        <x:v>1.1068783832475337</x:v>
       </x:c>
       <x:c r="E4" s="25" t="n">
-        <x:v>-0.010143792833782861</x:v>
+        <x:v>-0.007936294339388583</x:v>
       </x:c>
       <x:c r="F4" s="25" t="n">
-        <x:v>1.1187847370171302</x:v>
+        <x:v>1.1090858817419214</x:v>
       </x:c>
       <x:c r="G4" s="25" t="n">
-        <x:v>-0.01984264810898506</x:v>
+        <x:v>-0.0101437928337762</x:v>
+      </x:c>
+      <x:c r="H4" t="n">
+        <x:v>1.1187847370171313</x:v>
+      </x:c>
+      <x:c r="I4" t="n">
+        <x:v>-0.01984264810898617</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1259,16 +1678,22 @@
         <x:v>1.0492775325088857</x:v>
       </x:c>
       <x:c r="D5" s="25" t="n">
-        <x:v>1.047984614882784</x:v>
+        <x:v>1.1034364222819208</x:v>
       </x:c>
       <x:c r="E5" s="25" t="n">
-        <x:v>0.0012929176261016195</x:v>
+        <x:v>-0.05415888977303518</x:v>
       </x:c>
       <x:c r="F5" s="25" t="n">
-        <x:v>1.0538787794359854</x:v>
+        <x:v>1.0479846148827774</x:v>
       </x:c>
       <x:c r="G5" s="25" t="n">
-        <x:v>-0.004601246927099734</x:v>
+        <x:v>0.0012929176261082809</x:v>
+      </x:c>
+      <x:c r="H5" t="n">
+        <x:v>1.053878779435986</x:v>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>-0.0046012469271004</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1282,16 +1707,22 @@
         <x:v>1.051190068407256</x:v>
       </x:c>
       <x:c r="D6" s="25" t="n">
-        <x:v>1.0418021904874104</x:v>
+        <x:v>1.0999944613163077</x:v>
       </x:c>
       <x:c r="E6" s="25" t="n">
-        <x:v>0.009387877919845522</x:v>
+        <x:v>-0.04880439290905181</x:v>
       </x:c>
       <x:c r="F6" s="25" t="n">
-        <x:v>1.0633485169910277</x:v>
+        <x:v>1.0418021904874042</x:v>
       </x:c>
       <x:c r="G6" s="25" t="n">
-        <x:v>-0.012158448583771797</x:v>
+        <x:v>0.00938787791985174</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>1.0633485169910282</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>-0.012158448583772241</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1305,15 +1736,21 @@
         <x:v>1.037521695621621</x:v>
       </x:c>
       <x:c r="D7" s="25" t="n">
-        <x:v>1.0590700918847753</x:v>
+        <x:v>1.0965525003506946</x:v>
       </x:c>
       <x:c r="E7" s="25" t="n">
-        <x:v>-0.02154839626315419</x:v>
+        <x:v>-0.059030804729073516</x:v>
       </x:c>
       <x:c r="F7" s="25" t="n">
+        <x:v>1.0590700918847684</x:v>
+      </x:c>
+      <x:c r="G7" s="25" t="n">
+        <x:v>-0.021548396263147307</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
         <x:v>1.0607584226984088</x:v>
       </x:c>
-      <x:c r="G7" s="25" t="n">
+      <x:c r="I7" t="n">
         <x:v>-0.0232367270767877</x:v>
       </x:c>
     </x:row>
@@ -1328,15 +1765,21 @@
         <x:v>1.013552413411938</x:v>
       </x:c>
       <x:c r="D8" s="25" t="n">
-        <x:v>1.0145840997437725</x:v>
+        <x:v>1.0931105393850815</x:v>
       </x:c>
       <x:c r="E8" s="25" t="n">
-        <x:v>-0.0010316863318344804</x:v>
+        <x:v>-0.07955812597314349</x:v>
       </x:c>
       <x:c r="F8" s="25" t="n">
+        <x:v>1.0145840997437658</x:v>
+      </x:c>
+      <x:c r="G8" s="25" t="n">
+        <x:v>-0.001031686331827819</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
         <x:v>1.0167780898636596</x:v>
       </x:c>
-      <x:c r="G8" s="25" t="n">
+      <x:c r="I8" t="n">
         <x:v>-0.0032256764517215597</x:v>
       </x:c>
     </x:row>
@@ -1351,16 +1794,22 @@
         <x:v>1.0148546155541665</x:v>
       </x:c>
       <x:c r="D9" s="25" t="n">
-        <x:v>1.079337063076629</x:v>
+        <x:v>1.0896685784194686</x:v>
       </x:c>
       <x:c r="E9" s="25" t="n">
-        <x:v>-0.06448244752246257</x:v>
+        <x:v>-0.07481396286530217</x:v>
       </x:c>
       <x:c r="F9" s="25" t="n">
-        <x:v>1.06366211104731</x:v>
+        <x:v>1.0793370630766224</x:v>
       </x:c>
       <x:c r="G9" s="25" t="n">
-        <x:v>-0.04880749549314345</x:v>
+        <x:v>-0.06448244752245591</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>1.0636621110473097</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>-0.04880749549314323</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1374,16 +1823,22 @@
         <x:v>1.028916887976166</x:v>
       </x:c>
       <x:c r="D10" s="25" t="n">
-        <x:v>1.0950907922029667</x:v>
+        <x:v>1.0862266174538555</x:v>
       </x:c>
       <x:c r="E10" s="25" t="n">
-        <x:v>-0.06617390422680058</x:v>
+        <x:v>-0.05730972947768942</x:v>
       </x:c>
       <x:c r="F10" s="25" t="n">
-        <x:v>1.084268951586611</x:v>
+        <x:v>1.0950907922029598</x:v>
       </x:c>
       <x:c r="G10" s="25" t="n">
-        <x:v>-0.05535206361044498</x:v>
+        <x:v>-0.0661739042267937</x:v>
+      </x:c>
+      <x:c r="H10" t="n">
+        <x:v>1.0842689515866104</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>-0.05535206361044431</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1397,16 +1852,22 @@
         <x:v>1.1994769264243423</x:v>
       </x:c>
       <x:c r="D11" s="25" t="n">
-        <x:v>1.1732704988963603</x:v>
+        <x:v>1.0827846564882424</x:v>
       </x:c>
       <x:c r="E11" s="25" t="n">
-        <x:v>0.02620642752798208</x:v>
+        <x:v>0.11669226993609993</x:v>
       </x:c>
       <x:c r="F11" s="25" t="n">
-        <x:v>1.1588821248984404</x:v>
+        <x:v>1.1732704988963532</x:v>
       </x:c>
       <x:c r="G11" s="25" t="n">
-        <x:v>0.04059480152590189</x:v>
+        <x:v>0.026206427527989185</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>1.1588821248984391</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>0.040594801525903224</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1420,16 +1881,22 @@
         <x:v>1.369412016597778</x:v>
       </x:c>
       <x:c r="D12" s="25" t="n">
-        <x:v>1.103696253603714</x:v>
+        <x:v>1.0793426955226293</x:v>
       </x:c>
       <x:c r="E12" s="25" t="n">
-        <x:v>0.26571576299406385</x:v>
+        <x:v>0.2900693210751486</x:v>
       </x:c>
       <x:c r="F12" s="25" t="n">
-        <x:v>1.107520712626925</x:v>
+        <x:v>1.1036962536037072</x:v>
       </x:c>
       <x:c r="G12" s="25" t="n">
-        <x:v>0.2618913039708528</x:v>
+        <x:v>0.26571576299407074</x:v>
+      </x:c>
+      <x:c r="H12" t="n">
+        <x:v>1.1075207126269238</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>0.26189130397085414</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1443,16 +1910,22 @@
         <x:v>1.0405238169568338</x:v>
       </x:c>
       <x:c r="D13" s="25" t="n">
-        <x:v>1.064605116608867</x:v>
+        <x:v>1.0759007345570164</x:v>
       </x:c>
       <x:c r="E13" s="25" t="n">
-        <x:v>-0.024081299652033206</x:v>
+        <x:v>-0.03537691760018258</x:v>
       </x:c>
       <x:c r="F13" s="25" t="n">
-        <x:v>1.073688474049283</x:v>
+        <x:v>1.0646051166088604</x:v>
       </x:c>
       <x:c r="G13" s="25" t="n">
-        <x:v>-0.03316465709244909</x:v>
+        <x:v>-0.024081299652026544</x:v>
+      </x:c>
+      <x:c r="H13" t="n">
+        <x:v>1.0736884740492814</x:v>
+      </x:c>
+      <x:c r="I13" t="n">
+        <x:v>-0.033164657092447536</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1466,16 +1939,22 @@
         <x:v>1.0024350286026338</x:v>
       </x:c>
       <x:c r="D14" s="25" t="n">
-        <x:v>1.055693953132455</x:v>
+        <x:v>1.0724587735914033</x:v>
       </x:c>
       <x:c r="E14" s="25" t="n">
-        <x:v>-0.05325892452982117</x:v>
+        <x:v>-0.07002374498876951</x:v>
       </x:c>
       <x:c r="F14" s="25" t="n">
-        <x:v>1.0575810381627289</x:v>
+        <x:v>1.0556939531324483</x:v>
       </x:c>
       <x:c r="G14" s="25" t="n">
-        <x:v>-0.05514600956009508</x:v>
+        <x:v>-0.05325892452981451</x:v>
+      </x:c>
+      <x:c r="H14" t="n">
+        <x:v>1.057581038162727</x:v>
+      </x:c>
+      <x:c r="I14" t="n">
+        <x:v>-0.0551460095600933</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1489,16 +1968,22 @@
         <x:v>1.0132370548019292</x:v>
       </x:c>
       <x:c r="D15" s="25" t="n">
-        <x:v>1.0762254012108246</x:v>
+        <x:v>1.0690168126257902</x:v>
       </x:c>
       <x:c r="E15" s="25" t="n">
-        <x:v>-0.06298834640889539</x:v>
+        <x:v>-0.05577975782386102</x:v>
       </x:c>
       <x:c r="F15" s="25" t="n">
-        <x:v>1.072640165115477</x:v>
+        <x:v>1.0762254012108183</x:v>
       </x:c>
       <x:c r="G15" s="25" t="n">
-        <x:v>-0.05940311031354795</x:v>
+        <x:v>-0.06298834640888917</x:v>
+      </x:c>
+      <x:c r="H15" t="n">
+        <x:v>1.072640165115475</x:v>
+      </x:c>
+      <x:c r="I15" t="n">
+        <x:v>-0.05940311031354595</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1512,16 +1997,22 @@
         <x:v>1.1347291152233705</x:v>
       </x:c>
       <x:c r="D16" s="25" t="n">
-        <x:v>1.093568679982433</x:v>
+        <x:v>1.0567443519694384</x:v>
       </x:c>
       <x:c r="E16" s="25" t="n">
-        <x:v>0.0411604352409376</x:v>
+        <x:v>0.07798476325393211</x:v>
       </x:c>
       <x:c r="F16" s="25" t="n">
-        <x:v>1.0623085044494178</x:v>
+        <x:v>1.0935686799824267</x:v>
       </x:c>
       <x:c r="G16" s="25" t="n">
-        <x:v>0.07242061077395268</x:v>
+        <x:v>0.041160435240943816</x:v>
+      </x:c>
+      <x:c r="H16" t="n">
+        <x:v>1.0623085044494198</x:v>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>0.07242061077395068</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1535,16 +2026,22 @@
         <x:v>1.148258907235732</x:v>
       </x:c>
       <x:c r="D17" s="25" t="n">
-        <x:v>1.0852249028771592</x:v>
+        <x:v>1.0533023910038253</x:v>
       </x:c>
       <x:c r="E17" s="25" t="n">
-        <x:v>0.06303400435857287</x:v>
+        <x:v>0.09495651623190682</x:v>
       </x:c>
       <x:c r="F17" s="25" t="n">
-        <x:v>1.0615777913862072</x:v>
+        <x:v>1.0852249028771523</x:v>
       </x:c>
       <x:c r="G17" s="25" t="n">
-        <x:v>0.08668111584952487</x:v>
+        <x:v>0.06303400435857975</x:v>
+      </x:c>
+      <x:c r="H17" t="n">
+        <x:v>1.0615777913862086</x:v>
+      </x:c>
+      <x:c r="I17" t="n">
+        <x:v>0.08668111584952354</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1558,16 +2055,22 @@
         <x:v>1.0527034136913085</x:v>
       </x:c>
       <x:c r="D18" s="25" t="n">
-        <x:v>1.049310939304291</x:v>
+        <x:v>1.0498604300382122</x:v>
       </x:c>
       <x:c r="E18" s="25" t="n">
-        <x:v>0.003392474387017508</x:v>
+        <x:v>0.0028429836530963204</x:v>
       </x:c>
       <x:c r="F18" s="25" t="n">
-        <x:v>1.025500307218219</x:v>
+        <x:v>1.0493109393042843</x:v>
       </x:c>
       <x:c r="G18" s="25" t="n">
-        <x:v>0.027203106473089544</x:v>
+        <x:v>0.003392474387024169</x:v>
+      </x:c>
+      <x:c r="H18" t="n">
+        <x:v>1.02550030721822</x:v>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>0.027203106473088434</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1581,16 +2084,22 @@
         <x:v>0.9942628013708532</x:v>
       </x:c>
       <x:c r="D19" s="25" t="n">
-        <x:v>1.0590083125654883</x:v>
+        <x:v>1.0464184690725993</x:v>
       </x:c>
       <x:c r="E19" s="25" t="n">
-        <x:v>-0.06474551119463512</x:v>
+        <x:v>-0.05215566770174607</x:v>
       </x:c>
       <x:c r="F19" s="25" t="n">
-        <x:v>1.0472717306021073</x:v>
+        <x:v>1.0590083125654814</x:v>
       </x:c>
       <x:c r="G19" s="25" t="n">
-        <x:v>-0.05300892923125411</x:v>
+        <x:v>-0.06474551119462824</x:v>
+      </x:c>
+      <x:c r="H19" t="n">
+        <x:v>1.047271730602108</x:v>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>-0.053008929231254776</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1604,16 +2113,22 @@
         <x:v>0.987358874873832</x:v>
       </x:c>
       <x:c r="D20" s="25" t="n">
-        <x:v>1.0401593915938787</x:v>
+        <x:v>1.0429765081069862</x:v>
       </x:c>
       <x:c r="E20" s="25" t="n">
-        <x:v>-0.05280051672004671</x:v>
+        <x:v>-0.05561763323315416</x:v>
       </x:c>
       <x:c r="F20" s="25" t="n">
-        <x:v>1.0837828115895174</x:v>
+        <x:v>1.0401593915938718</x:v>
       </x:c>
       <x:c r="G20" s="25" t="n">
-        <x:v>-0.09642393671568539</x:v>
+        <x:v>-0.052800516720039825</x:v>
+      </x:c>
+      <x:c r="H20" t="n">
+        <x:v>1.083782811589518</x:v>
+      </x:c>
+      <x:c r="I20" t="n">
+        <x:v>-0.09642393671568605</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1627,16 +2142,22 @@
         <x:v>0.9863446971064622</x:v>
       </x:c>
       <x:c r="D21" s="25" t="n">
-        <x:v>1.0318743558428782</x:v>
+        <x:v>1.039534547141373</x:v>
       </x:c>
       <x:c r="E21" s="25" t="n">
-        <x:v>-0.04552965873641601</x:v>
+        <x:v>-0.053189850034910835</x:v>
       </x:c>
       <x:c r="F21" s="25" t="n">
-        <x:v>1.0621460261311941</x:v>
+        <x:v>1.0318743558428713</x:v>
       </x:c>
       <x:c r="G21" s="25" t="n">
-        <x:v>-0.07580132902473191</x:v>
+        <x:v>-0.04552965873640913</x:v>
+      </x:c>
+      <x:c r="H21" t="n">
+        <x:v>1.0621460261311946</x:v>
+      </x:c>
+      <x:c r="I21" t="n">
+        <x:v>-0.07580132902473236</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1650,16 +2171,22 @@
         <x:v>0.9583125714612186</x:v>
       </x:c>
       <x:c r="D22" s="25" t="n">
-        <x:v>1.035227275941853</x:v>
+        <x:v>1.03609258617576</x:v>
       </x:c>
       <x:c r="E22" s="25" t="n">
-        <x:v>-0.07691470448063442</x:v>
+        <x:v>-0.07778001471454132</x:v>
       </x:c>
       <x:c r="F22" s="25" t="n">
-        <x:v>1.0460889207135182</x:v>
+        <x:v>1.0352272759418457</x:v>
       </x:c>
       <x:c r="G22" s="25" t="n">
-        <x:v>-0.0877763492522996</x:v>
+        <x:v>-0.0769147044806271</x:v>
+      </x:c>
+      <x:c r="H22" t="n">
+        <x:v>1.046088920713518</x:v>
+      </x:c>
+      <x:c r="I22" t="n">
+        <x:v>-0.08777634925229938</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1673,16 +2200,22 @@
         <x:v>0.9623791321782756</x:v>
       </x:c>
       <x:c r="D23" s="25" t="n">
-        <x:v>1.0287193903307992</x:v>
+        <x:v>1.032650625210147</x:v>
       </x:c>
       <x:c r="E23" s="25" t="n">
-        <x:v>-0.06634025815252353</x:v>
+        <x:v>-0.07027149303187141</x:v>
       </x:c>
       <x:c r="F23" s="25" t="n">
-        <x:v>1.0085358540550484</x:v>
+        <x:v>1.0287193903307918</x:v>
       </x:c>
       <x:c r="G23" s="25" t="n">
-        <x:v>-0.04615672187677278</x:v>
+        <x:v>-0.06634025815251621</x:v>
+      </x:c>
+      <x:c r="H23" t="n">
+        <x:v>1.008535854055048</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>-0.04615672187677233</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1696,16 +2229,22 @@
         <x:v>0.9697997580034412</x:v>
       </x:c>
       <x:c r="D24" s="25" t="n">
-        <x:v>1.0364820312504948</x:v>
+        <x:v>1.029208664244534</x:v>
       </x:c>
       <x:c r="E24" s="25" t="n">
-        <x:v>-0.06668227324705356</x:v>
+        <x:v>-0.05940890624109274</x:v>
       </x:c>
       <x:c r="F24" s="25" t="n">
-        <x:v>1.014510053029753</x:v>
+        <x:v>1.0364820312504872</x:v>
       </x:c>
       <x:c r="G24" s="25" t="n">
-        <x:v>-0.04471029502631185</x:v>
+        <x:v>-0.06668227324704601</x:v>
+      </x:c>
+      <x:c r="H24" t="n">
+        <x:v>1.0145100530297522</x:v>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>-0.044710295026310964</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1719,16 +2258,22 @@
         <x:v>1.121446863275139</x:v>
       </x:c>
       <x:c r="D25" s="25" t="n">
-        <x:v>1.1377164055225402</x:v>
+        <x:v>1.0257667032789208</x:v>
       </x:c>
       <x:c r="E25" s="25" t="n">
-        <x:v>-0.01626954224740107</x:v>
+        <x:v>0.09568015999621826</x:v>
       </x:c>
       <x:c r="F25" s="25" t="n">
-        <x:v>1.1139964103099447</x:v>
+        <x:v>1.1377164055225322</x:v>
       </x:c>
       <x:c r="G25" s="25" t="n">
-        <x:v>0.007450452965194421</x:v>
+        <x:v>-0.016269542247393076</x:v>
+      </x:c>
+      <x:c r="H25" t="n">
+        <x:v>1.1139964103099431</x:v>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>0.007450452965195975</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1742,16 +2287,22 @@
         <x:v>1.2753481624898797</x:v>
       </x:c>
       <x:c r="D26" s="25" t="n">
-        <x:v>1.0811430046419068</x:v>
+        <x:v>1.0223247423133077</x:v>
       </x:c>
       <x:c r="E26" s="25" t="n">
-        <x:v>0.19420515784797288</x:v>
+        <x:v>0.253023420176572</x:v>
       </x:c>
       <x:c r="F26" s="25" t="n">
-        <x:v>1.1130078021261454</x:v>
+        <x:v>1.0811430046418993</x:v>
       </x:c>
       <x:c r="G26" s="25" t="n">
-        <x:v>0.16234036036373434</x:v>
+        <x:v>0.19420515784798043</x:v>
+      </x:c>
+      <x:c r="H26" t="n">
+        <x:v>1.1130078021261434</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>0.16234036036373634</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1765,16 +2316,22 @@
         <x:v>1.0110435026247482</x:v>
       </x:c>
       <x:c r="D27" s="25" t="n">
-        <x:v>0.8984074277434225</x:v>
+        <x:v>1.0188827813476948</x:v>
       </x:c>
       <x:c r="E27" s="25" t="n">
-        <x:v>0.11263607488132565</x:v>
+        <x:v>-0.007839278722946652</x:v>
       </x:c>
       <x:c r="F27" s="25" t="n">
-        <x:v>0.9547609628861833</x:v>
+        <x:v>0.8984074277434159</x:v>
       </x:c>
       <x:c r="G27" s="25" t="n">
-        <x:v>0.056282539738564896</x:v>
+        <x:v>0.11263607488133232</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>0.954760962886182</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>0.05628253973856623</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1788,16 +2345,22 @@
         <x:v>0.944085367734204</x:v>
       </x:c>
       <x:c r="D28" s="25" t="n">
-        <x:v>0.9515781670032919</x:v>
+        <x:v>1.0154408203820817</x:v>
       </x:c>
       <x:c r="E28" s="25" t="n">
-        <x:v>-0.0074927992690878575</x:v>
+        <x:v>-0.07135545264787768</x:v>
       </x:c>
       <x:c r="F28" s="25" t="n">
-        <x:v>0.947556333341345</x:v>
+        <x:v>0.9515781670032848</x:v>
       </x:c>
       <x:c r="G28" s="25" t="n">
-        <x:v>-0.0034709656071409967</x:v>
+        <x:v>-0.007492799269080752</x:v>
+      </x:c>
+      <x:c r="H28" t="n">
+        <x:v>0.9475563333413435</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>-0.0034709656071394424</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1811,16 +2374,22 @@
         <x:v>0.9351293124328952</x:v>
       </x:c>
       <x:c r="D29" s="25" t="n">
-        <x:v>0.9527821951010453</x:v>
+        <x:v>1.0119988594164686</x:v>
       </x:c>
       <x:c r="E29" s="25" t="n">
-        <x:v>-0.017652882668150127</x:v>
+        <x:v>-0.0768695469835734</x:v>
       </x:c>
       <x:c r="F29" s="25" t="n">
-        <x:v>0.9401589718627597</x:v>
+        <x:v>0.9527821951010383</x:v>
       </x:c>
       <x:c r="G29" s="25" t="n">
-        <x:v>-0.0050296594298644415</x:v>
+        <x:v>-0.017652882668143133</x:v>
+      </x:c>
+      <x:c r="H29" t="n">
+        <x:v>0.9401589718627579</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>-0.005029659429862665</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1834,16 +2403,22 @@
         <x:v>1.0969896438602886</x:v>
       </x:c>
       <x:c r="D30" s="25" t="n">
-        <x:v>1.1375911339606488</x:v>
+        <x:v>1.053408052897227</x:v>
       </x:c>
       <x:c r="E30" s="25" t="n">
-        <x:v>-0.04060149010036018</x:v>
+        <x:v>0.04358159096306169</x:v>
       </x:c>
       <x:c r="F30" s="25" t="n">
-        <x:v>1.118377755206173</x:v>
+        <x:v>1.1375911339606424</x:v>
       </x:c>
       <x:c r="G30" s="25" t="n">
-        <x:v>-0.021388111345884475</x:v>
+        <x:v>-0.04060149010035374</x:v>
+      </x:c>
+      <x:c r="H30" t="n">
+        <x:v>1.1183777552061747</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>-0.02138811134588603</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1857,16 +2432,22 @@
         <x:v>1.083291954810638</x:v>
       </x:c>
       <x:c r="D31" s="25" t="n">
-        <x:v>0.9891844474928064</x:v>
+        <x:v>1.049966091931614</x:v>
       </x:c>
       <x:c r="E31" s="25" t="n">
-        <x:v>0.09410750731783146</x:v>
+        <x:v>0.03332586287902384</x:v>
       </x:c>
       <x:c r="F31" s="25" t="n">
-        <x:v>1.0301173384842712</x:v>
+        <x:v>0.9891844474928002</x:v>
       </x:c>
       <x:c r="G31" s="25" t="n">
-        <x:v>0.053174616326366664</x:v>
+        <x:v>0.09410750731783768</x:v>
+      </x:c>
+      <x:c r="H31" t="n">
+        <x:v>1.0301173384842723</x:v>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>0.053174616326365554</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1880,16 +2461,22 @@
         <x:v>1.012812316054036</x:v>
       </x:c>
       <x:c r="D32" s="25" t="n">
-        <x:v>0.9856123883306369</x:v>
+        <x:v>1.046524130966001</x:v>
       </x:c>
       <x:c r="E32" s="25" t="n">
-        <x:v>0.027199927723399187</x:v>
+        <x:v>-0.033711814911964844</x:v>
       </x:c>
       <x:c r="F32" s="25" t="n">
-        <x:v>1.0285604641312944</x:v>
+        <x:v>0.9856123883306306</x:v>
       </x:c>
       <x:c r="G32" s="25" t="n">
-        <x:v>-0.015748148077258328</x:v>
+        <x:v>0.027199927723405515</x:v>
+      </x:c>
+      <x:c r="H32" t="n">
+        <x:v>1.0285604641312949</x:v>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>-0.015748148077258772</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1903,16 +2490,22 @@
         <x:v>1.0025049341624674</x:v>
       </x:c>
       <x:c r="D33" s="25" t="n">
-        <x:v>0.9907930918021848</x:v>
+        <x:v>1.0430821700003878</x:v>
       </x:c>
       <x:c r="E33" s="25" t="n">
-        <x:v>0.011711842360282665</x:v>
+        <x:v>-0.04057723583792039</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
-        <x:v>1.0114869887687483</x:v>
+        <x:v>0.9907930918021788</x:v>
       </x:c>
       <x:c r="G33" s="25" t="n">
-        <x:v>-0.008982054606280876</x:v>
+        <x:v>0.01171184236028866</x:v>
+      </x:c>
+      <x:c r="H33" t="n">
+        <x:v>1.0114869887687488</x:v>
+      </x:c>
+      <x:c r="I33" t="n">
+        <x:v>-0.00898205460628132</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1926,16 +2519,22 @@
         <x:v>0.97553166012387</x:v>
       </x:c>
       <x:c r="D34" s="25" t="n">
-        <x:v>1.0016495780595571</x:v>
+        <x:v>1.0396402090347747</x:v>
       </x:c>
       <x:c r="E34" s="25" t="n">
-        <x:v>-0.026117917935687074</x:v>
+        <x:v>-0.06410854891090467</x:v>
       </x:c>
       <x:c r="F34" s="25" t="n">
-        <x:v>1.0112466678005039</x:v>
+        <x:v>1.0016495780595507</x:v>
       </x:c>
       <x:c r="G34" s="25" t="n">
-        <x:v>-0.035715007676633825</x:v>
+        <x:v>-0.026117917935680635</x:v>
+      </x:c>
+      <x:c r="H34" t="n">
+        <x:v>1.011246667800504</x:v>
+      </x:c>
+      <x:c r="I34" t="n">
+        <x:v>-0.03571500767663405</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1949,16 +2548,22 @@
         <x:v>0.9692931924059508</x:v>
       </x:c>
       <x:c r="D35" s="25" t="n">
-        <x:v>1.0036395872340838</x:v>
+        <x:v>1.0361982480691618</x:v>
       </x:c>
       <x:c r="E35" s="25" t="n">
-        <x:v>-0.03434639482813295</x:v>
+        <x:v>-0.06690505566321103</x:v>
       </x:c>
       <x:c r="F35" s="25" t="n">
-        <x:v>1.0027948439411876</x:v>
+        <x:v>1.0036395872340778</x:v>
       </x:c>
       <x:c r="G35" s="25" t="n">
-        <x:v>-0.033501651535236765</x:v>
+        <x:v>-0.03434639482812696</x:v>
+      </x:c>
+      <x:c r="H35" t="n">
+        <x:v>1.0027948439411878</x:v>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:v>-0.03350165153523699</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1972,16 +2577,22 @@
         <x:v>0.9577101612387616</x:v>
       </x:c>
       <x:c r="D36" s="25" t="n">
-        <x:v>1.0026754957689545</x:v>
+        <x:v>1.0327562871035487</x:v>
       </x:c>
       <x:c r="E36" s="25" t="n">
-        <x:v>-0.04496533453019291</x:v>
+        <x:v>-0.0750461258647871</x:v>
       </x:c>
       <x:c r="F36" s="25" t="n">
-        <x:v>0.9915049071876945</x:v>
+        <x:v>1.0026754957689485</x:v>
       </x:c>
       <x:c r="G36" s="25" t="n">
-        <x:v>-0.033794745948932836</x:v>
+        <x:v>-0.04496533453018692</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>0.9915049071876944</x:v>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>-0.033794745948932725</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1995,16 +2606,22 @@
         <x:v>0.9717110858523637</x:v>
       </x:c>
       <x:c r="D37" s="25" t="n">
-        <x:v>1.0217915710064795</x:v>
+        <x:v>1.0293143261379356</x:v>
       </x:c>
       <x:c r="E37" s="25" t="n">
-        <x:v>-0.050080485154115895</x:v>
+        <x:v>-0.057603240285571955</x:v>
       </x:c>
       <x:c r="F37" s="25" t="n">
-        <x:v>1.0007653483145145</x:v>
+        <x:v>1.0217915710064733</x:v>
       </x:c>
       <x:c r="G37" s="25" t="n">
-        <x:v>-0.029054262462150815</x:v>
+        <x:v>-0.05008048515410968</x:v>
+      </x:c>
+      <x:c r="H37" t="n">
+        <x:v>1.000765348314514</x:v>
+      </x:c>
+      <x:c r="I37" t="n">
+        <x:v>-0.02905426246215037</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2018,16 +2635,22 @@
         <x:v>0.9764503159103964</x:v>
       </x:c>
       <x:c r="D38" s="25" t="n">
-        <x:v>0.9895250642790621</x:v>
+        <x:v>1.0258723651723227</x:v>
       </x:c>
       <x:c r="E38" s="25" t="n">
-        <x:v>-0.013074748368665623</x:v>
+        <x:v>-0.04942204926192628</x:v>
       </x:c>
       <x:c r="F38" s="25" t="n">
-        <x:v>0.9673943351749301</x:v>
+        <x:v>0.9895250642790558</x:v>
       </x:c>
       <x:c r="G38" s="25" t="n">
-        <x:v>0.009055980735466318</x:v>
+        <x:v>-0.013074748368659406</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>0.9673943351749296</x:v>
+      </x:c>
+      <x:c r="I38" t="n">
+        <x:v>0.009055980735466873</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2041,16 +2664,22 @@
         <x:v>1.1551925165753971</x:v>
       </x:c>
       <x:c r="D39" s="25" t="n">
-        <x:v>1.1015853220959813</x:v>
+        <x:v>1.0224304042067096</x:v>
       </x:c>
       <x:c r="E39" s="25" t="n">
-        <x:v>0.053607194479415865</x:v>
+        <x:v>0.1327621123686875</x:v>
       </x:c>
       <x:c r="F39" s="25" t="n">
-        <x:v>1.0507468438895216</x:v>
+        <x:v>1.1015853220959748</x:v>
       </x:c>
       <x:c r="G39" s="25" t="n">
-        <x:v>0.10444567268587557</x:v>
+        <x:v>0.053607194479422304</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>1.0507468438895202</x:v>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>0.1044456726858769</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2064,16 +2693,22 @@
         <x:v>1.3669555213498588</x:v>
       </x:c>
       <x:c r="D40" s="25" t="n">
-        <x:v>1.0404410302737837</x:v>
+        <x:v>1.0189884432410965</x:v>
       </x:c>
       <x:c r="E40" s="25" t="n">
-        <x:v>0.3265144910760751</x:v>
+        <x:v>0.34796707810876226</x:v>
       </x:c>
       <x:c r="F40" s="25" t="n">
-        <x:v>1.005797163130628</x:v>
+        <x:v>1.0404410302737777</x:v>
       </x:c>
       <x:c r="G40" s="25" t="n">
-        <x:v>0.3611583582192308</x:v>
+        <x:v>0.3265144910760811</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>1.0057971631306266</x:v>
+      </x:c>
+      <x:c r="I40" t="n">
+        <x:v>0.36115835821923215</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2087,16 +2722,22 @@
         <x:v>0.9935083561243656</x:v>
       </x:c>
       <x:c r="D41" s="25" t="n">
-        <x:v>1.0430764054088477</x:v>
+        <x:v>1.0155464822754834</x:v>
       </x:c>
       <x:c r="E41" s="25" t="n">
-        <x:v>-0.04956804928448211</x:v>
+        <x:v>-0.022038126151117776</x:v>
       </x:c>
       <x:c r="F41" s="25" t="n">
-        <x:v>1.0501725120252954</x:v>
+        <x:v>1.0430764054088417</x:v>
       </x:c>
       <x:c r="G41" s="25" t="n">
-        <x:v>-0.05666415590092977</x:v>
+        <x:v>-0.04956804928447611</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>1.0501725120252936</x:v>
+      </x:c>
+      <x:c r="I41" t="n">
+        <x:v>-0.05666415590092799</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2110,16 +2751,22 @@
         <x:v>0.9182138012885724</x:v>
       </x:c>
       <x:c r="D42" s="25" t="n">
-        <x:v>1.050565597529023</x:v>
+        <x:v>1.0121045213098705</x:v>
       </x:c>
       <x:c r="E42" s="25" t="n">
-        <x:v>-0.13235179624045046</x:v>
+        <x:v>-0.09389072002129806</x:v>
       </x:c>
       <x:c r="F42" s="25" t="n">
-        <x:v>1.0767457493347872</x:v>
+        <x:v>1.0505655975290171</x:v>
       </x:c>
       <x:c r="G42" s="25" t="n">
-        <x:v>-0.15853194804621473</x:v>
+        <x:v>-0.13235179624044469</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>1.0767457493347852</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>-0.15853194804621273</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2133,16 +2780,1724 @@
         <x:v>0.9543288329334304</x:v>
       </x:c>
       <x:c r="D43" s="25" t="n">
-        <x:v>1.0763635794484676</x:v>
+        <x:v>1.0086625603442574</x:v>
       </x:c>
       <x:c r="E43" s="25" t="n">
-        <x:v>-0.1220347465150372</x:v>
+        <x:v>-0.05433372741082698</x:v>
       </x:c>
       <x:c r="F43" s="25" t="n">
-        <x:v>1.088783375300857</x:v>
+        <x:v>1.0763635794484612</x:v>
       </x:c>
       <x:c r="G43" s="25" t="n">
-        <x:v>-0.1344545423674265</x:v>
+        <x:v>-0.12203474651503077</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>1.0887833753008542</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:v>-0.13445454236742382</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>Exposed_mean_of_region_means</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Comparison_mean_of_region_means</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>Difference_exposed_minus_comparison</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>Exposed_SD_across_regions</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>Comparison_SD_across_regions</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>Exact_permutation_p_region_means</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>Permutation_allocations</x:v>
+      </x:c>
+      <x:c r="I1" s="46" t="str">
+        <x:v>Welch_t_region_means</x:v>
+      </x:c>
+      <x:c r="J1" s="46" t="str">
+        <x:v>Welch_p_region_means</x:v>
+      </x:c>
+      <x:c r="K1" s="46" t="str">
+        <x:v>N_regions_exposed</x:v>
+      </x:c>
+      <x:c r="L1" s="46" t="str">
+        <x:v>N_regions_comparison</x:v>
+      </x:c>
+      <x:c r="M1" s="46" t="str">
+        <x:v>Period</x:v>
+      </x:c>
+      <x:c r="N1" s="46" t="str">
+        <x:v>N_region_year_rows</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Cancer_pct</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>0.29317857142857146</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>0.22587142857142858</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>0.06730714285714287</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>0.013108653085435058</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>0.07753063351123257</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I2" s="52" t="n">
+        <x:v>1.4826134040391095</x:v>
+      </x:c>
+      <x:c r="J2" s="52" t="n">
+        <x:v>0.269950464361062</x:v>
+      </x:c>
+      <x:c r="K2" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L2" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M2" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+      <x:c r="N2" s="52" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>0.8715357142857143</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>0.9162380952380952</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>-0.04470238095238088</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>0.10513479564398293</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>0.14690880020690153</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="n">
+        <x:v>-0.4285939227035905</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="n">
+        <x:v>0.6924560469237471</x:v>
+      </x:c>
+      <x:c r="K3" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L3" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M3" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+      <x:c r="N3" s="52" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>2.6672904761904763</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>2.472985714285714</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>0.1943047619047622</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>0.3989875059634901</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>0.27269120122308677</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I4" s="52" t="n">
+        <x:v>0.6963903131377864</x:v>
+      </x:c>
+      <x:c r="J4" s="52" t="n">
+        <x:v>0.5292485863440876</x:v>
+      </x:c>
+      <x:c r="K4" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L4" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M4" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+      <x:c r="N4" s="52" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>Disability_pct</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="n">
+        <x:v>4.186102380952381</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>3.9418023809523812</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>0.24429999999999952</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>0.502577594086954</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>0.8186925651247091</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I5" s="52" t="n">
+        <x:v>0.4404742008431818</x:v>
+      </x:c>
+      <x:c r="J5" s="52" t="n">
+        <x:v>0.6867169778742611</x:v>
+      </x:c>
+      <x:c r="K5" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L5" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M5" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+      <x:c r="N5" s="52" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="n">
+        <x:v>4.836159523809523</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>4.885714285714286</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>-0.049554761904762934</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>0.10178725721470562</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>0.07734431367038454</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="n">
+        <x:v>-0.6714024780755286</x:v>
+      </x:c>
+      <x:c r="J6" s="52" t="n">
+        <x:v>0.5412195046930761</x:v>
+      </x:c>
+      <x:c r="K6" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L6" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M6" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+      <x:c r="N6" s="52" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>Mortality_pct</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="n">
+        <x:v>1.0522654904053244</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>0.9406909369801051</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>0.11157455342521927</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>0.03392347674827029</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>0.22863812616588078</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="n">
+        <x:v>0.8360815928151607</x:v>
+      </x:c>
+      <x:c r="J7" s="52" t="n">
+        <x:v>0.48786498185618404</x:v>
+      </x:c>
+      <x:c r="K7" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L7" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M7" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+      <x:c r="N7" s="52" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="52" t="str">
+        <x:v>Cancer_pct</x:v>
+      </x:c>
+      <x:c r="B8" s="52" t="n">
+        <x:v>0.28414545454545453</x:v>
+      </x:c>
+      <x:c r="C8" s="52" t="n">
+        <x:v>0.22221212121212122</x:v>
+      </x:c>
+      <x:c r="D8" s="52" t="n">
+        <x:v>0.06193333333333331</x:v>
+      </x:c>
+      <x:c r="E8" s="52" t="n">
+        <x:v>0.018878014235814197</x:v>
+      </x:c>
+      <x:c r="F8" s="52" t="n">
+        <x:v>0.07357424559127378</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="52" t="n">
+        <x:v>1.4122583392917105</x:v>
+      </x:c>
+      <x:c r="J8" s="52" t="n">
+        <x:v>0.2797406907241236</x:v>
+      </x:c>
+      <x:c r="K8" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L8" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M8" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+      <x:c r="N8" s="52" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="52" t="str">
+        <x:v>Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="B9" s="52" t="n">
+        <x:v>0.9206060606060605</x:v>
+      </x:c>
+      <x:c r="C9" s="52" t="n">
+        <x:v>0.9456969696969697</x:v>
+      </x:c>
+      <x:c r="D9" s="52" t="n">
+        <x:v>-0.025090909090909164</x:v>
+      </x:c>
+      <x:c r="E9" s="52" t="n">
+        <x:v>0.1450728324730826</x:v>
+      </x:c>
+      <x:c r="F9" s="52" t="n">
+        <x:v>0.14503440268237225</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I9" s="52" t="n">
+        <x:v>-0.21185243409429325</x:v>
+      </x:c>
+      <x:c r="J9" s="52" t="n">
+        <x:v>0.8425790431975005</x:v>
+      </x:c>
+      <x:c r="K9" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L9" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M9" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+      <x:c r="N9" s="52" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="52" t="str">
+        <x:v>Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="B10" s="52" t="n">
+        <x:v>2.5210545454545454</x:v>
+      </x:c>
+      <x:c r="C10" s="52" t="n">
+        <x:v>2.3946818181818177</x:v>
+      </x:c>
+      <x:c r="D10" s="52" t="n">
+        <x:v>0.12637272727272775</x:v>
+      </x:c>
+      <x:c r="E10" s="52" t="n">
+        <x:v>0.39786789025903263</x:v>
+      </x:c>
+      <x:c r="F10" s="52" t="n">
+        <x:v>0.27449976079713784</x:v>
+      </x:c>
+      <x:c r="G10" s="52" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="H10" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I10" s="52" t="n">
+        <x:v>0.4528267183436079</x:v>
+      </x:c>
+      <x:c r="J10" s="52" t="n">
+        <x:v>0.6769313668165573</x:v>
+      </x:c>
+      <x:c r="K10" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L10" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M10" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+      <x:c r="N10" s="52" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="52" t="str">
+        <x:v>Disability_pct</x:v>
+      </x:c>
+      <x:c r="B11" s="52" t="n">
+        <x:v>4.16440303030303</x:v>
+      </x:c>
+      <x:c r="C11" s="52" t="n">
+        <x:v>4.099842424242425</x:v>
+      </x:c>
+      <x:c r="D11" s="52" t="n">
+        <x:v>0.06456060606060543</x:v>
+      </x:c>
+      <x:c r="E11" s="52" t="n">
+        <x:v>0.47843563660607025</x:v>
+      </x:c>
+      <x:c r="F11" s="52" t="n">
+        <x:v>1.1245248528403664</x:v>
+      </x:c>
+      <x:c r="G11" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I11" s="52" t="n">
+        <x:v>0.0915022752723452</x:v>
+      </x:c>
+      <x:c r="J11" s="52" t="n">
+        <x:v>0.9334493459846925</x:v>
+      </x:c>
+      <x:c r="K11" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L11" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M11" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+      <x:c r="N11" s="52" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="52" t="str">
+        <x:v>Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="B12" s="52" t="n">
+        <x:v>4.909090909090909</x:v>
+      </x:c>
+      <x:c r="C12" s="52" t="n">
+        <x:v>4.927272727272727</x:v>
+      </x:c>
+      <x:c r="D12" s="52" t="n">
+        <x:v>-0.018181818181817633</x:v>
+      </x:c>
+      <x:c r="E12" s="52" t="n">
+        <x:v>0.05061603966209141</x:v>
+      </x:c>
+      <x:c r="F12" s="52" t="n">
+        <x:v>0.08294676177679389</x:v>
+      </x:c>
+      <x:c r="G12" s="52" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H12" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I12" s="52" t="n">
+        <x:v>-0.32408767757677076</x:v>
+      </x:c>
+      <x:c r="J12" s="52" t="n">
+        <x:v>0.76529764910498</x:v>
+      </x:c>
+      <x:c r="K12" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L12" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M12" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+      <x:c r="N12" s="52" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="52" t="str">
+        <x:v>Mortality_pct</x:v>
+      </x:c>
+      <x:c r="B13" s="52" t="n">
+        <x:v>1.0722013795007277</x:v>
+      </x:c>
+      <x:c r="C13" s="52" t="n">
+        <x:v>0.965806569333775</x:v>
+      </x:c>
+      <x:c r="D13" s="52" t="n">
+        <x:v>0.10639481016695274</x:v>
+      </x:c>
+      <x:c r="E13" s="52" t="n">
+        <x:v>0.033793837099145276</x:v>
+      </x:c>
+      <x:c r="F13" s="52" t="n">
+        <x:v>0.23715402424023824</x:v>
+      </x:c>
+      <x:c r="G13" s="52" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="H13" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I13" s="52" t="n">
+        <x:v>0.769281796235483</x:v>
+      </x:c>
+      <x:c r="J13" s="52" t="n">
+        <x:v>0.5194217454725613</x:v>
+      </x:c>
+      <x:c r="K13" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L13" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M13" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+      <x:c r="N13" s="52" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>Exposed_mean_of_region_means</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Comparison_mean_of_region_means</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>Difference_exposed_minus_comparison</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>Exposed_SD_across_regions</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>Comparison_SD_across_regions</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>Exact_permutation_p_region_means</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>Permutation_allocations</x:v>
+      </x:c>
+      <x:c r="I1" s="46" t="str">
+        <x:v>Welch_t_region_means</x:v>
+      </x:c>
+      <x:c r="J1" s="46" t="str">
+        <x:v>Welch_p_region_means</x:v>
+      </x:c>
+      <x:c r="K1" s="46" t="str">
+        <x:v>N_regions_exposed</x:v>
+      </x:c>
+      <x:c r="L1" s="46" t="str">
+        <x:v>N_regions_comparison</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Cancer_pct</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>0.28414545454545453</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>0.22221212121212122</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>0.06193333333333331</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>0.018878014235814197</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>0.07357424559127378</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I2" s="52" t="n">
+        <x:v>1.4122583392917105</x:v>
+      </x:c>
+      <x:c r="J2" s="52" t="n">
+        <x:v>0.2797406907241236</x:v>
+      </x:c>
+      <x:c r="K2" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L2" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>0.9206060606060605</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>0.9456969696969697</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>-0.025090909090909164</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>0.1450728324730826</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>0.14503440268237225</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="n">
+        <x:v>-0.21185243409429325</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="n">
+        <x:v>0.8425790431975005</x:v>
+      </x:c>
+      <x:c r="K3" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L3" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>2.5210545454545454</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>2.3946818181818177</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>0.12637272727272775</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>0.39786789025903263</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>0.27449976079713784</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I4" s="52" t="n">
+        <x:v>0.4528267183436079</x:v>
+      </x:c>
+      <x:c r="J4" s="52" t="n">
+        <x:v>0.6769313668165573</x:v>
+      </x:c>
+      <x:c r="K4" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L4" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>Disability_pct</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="n">
+        <x:v>4.16440303030303</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>4.099842424242425</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>0.06456060606060543</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>0.47843563660607025</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>1.1245248528403664</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I5" s="52" t="n">
+        <x:v>0.0915022752723452</x:v>
+      </x:c>
+      <x:c r="J5" s="52" t="n">
+        <x:v>0.9334493459846925</x:v>
+      </x:c>
+      <x:c r="K5" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L5" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="n">
+        <x:v>4.909090909090909</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>4.927272727272727</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>-0.018181818181817633</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>0.05061603966209141</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>0.08294676177679389</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="n">
+        <x:v>-0.32408767757677076</x:v>
+      </x:c>
+      <x:c r="J6" s="52" t="n">
+        <x:v>0.76529764910498</x:v>
+      </x:c>
+      <x:c r="K6" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L6" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>Mortality_pct</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="n">
+        <x:v>1.0722013795007277</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>0.965806569333775</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>0.10639481016695274</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>0.033793837099145276</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>0.23715402424023824</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="n">
+        <x:v>0.769281796235483</x:v>
+      </x:c>
+      <x:c r="J7" s="52" t="n">
+        <x:v>0.5194217454725613</x:v>
+      </x:c>
+      <x:c r="K7" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L7" s="52" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Project_Group</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>Region</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Cancer_pct</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>Disability_pct</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>Mortality_pct</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Comparison-classified</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="str">
+        <x:v>Akmola</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>0.23989090909090907</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>0.8685454545454546</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>2.4308272727272726</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>3.868981818181818</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>4.981818181818182</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>1.0866480397558578</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Comparison-classified</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="str">
+        <x:v>Almaty Region</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>0.14140909090909093</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>0.8555454545454545</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>2.6493181818181815</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>5.321881818181819</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>4.831818181818182</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>0.6925712775646561</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>Comparison-classified</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="str">
+        <x:v>Kostanay</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>0.28533636363636367</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>1.113</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>2.1039</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>3.108663636363637</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>4.968181818181818</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>1.1182003906808111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>Exposed-classified</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>0.2878727272727273</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>1.076</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>2.965718181818182</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>4.074</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>4.963636363636364</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>1.1112052658427698</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>Exposed-classified</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>0.2636818181818182</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>0.8970909090909092</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>2.1987</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>4.681590909090909</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>4.863636363636363</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>1.0537222088099556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>Exposed-classified</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>0.3008818181818182</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>0.7887272727272727</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>2.398745454545455</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>3.7376181818181817</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>4.8999999999999995</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>1.0516766638494572</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Parameters</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>Adjusted_R2</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>RMSE</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>AIC</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>BIC</x:v>
+      </x:c>
+      <x:c r="I1" s="46" t="str">
+        <x:v>Period</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Baseline - Region + Year</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>0.08395152419528318</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>0.01163190768438449</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>0.10233318411823028</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>-64.28895057894854</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>-57.33827210581507</x:v>
+      </x:c>
+      <x:c r="I2" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Before PCA - 5 original indicators</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>0.3112406050470612</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>0.14426863051301542</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>0.08873419775528259</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>-66.26639648590324</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>-50.62736992135293</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>After PCA - PC1 + PC2</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>0.26392628806790863</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>0.16169382807734045</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>0.09173137705533681</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>-69.47598936276958</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>-59.04997165306937</x:v>
+      </x:c>
+      <x:c r="I4" s="52" t="str">
+        <x:v>2011-2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>Baseline - Region + Year</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>0.10514499160280866</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>0.012573783837582009</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>0.10476273795276436</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>-47.249827006041485</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>-41.263796760175566</x:v>
+      </x:c>
+      <x:c r="I5" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>Before PCA - 5 original indicators</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>0.5014954334092099</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>0.33532724454561325</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>0.07819249554967564</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>-56.55644246615573</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>-43.087874412957405</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>After PCA - PC1 + PC2</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>0.4713652325530965</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>0.3734699052481144</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>0.08052085260474846</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>-60.61983671773642</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>-51.64079134893754</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="str">
+        <x:v>2011-2021</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Parameters</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>Adjusted_R2</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>RMSE</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>AIC</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>BIC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Baseline - Region + Year</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>0.10514499160280866</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>0.012573783837582009</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>0.10476273795276436</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>-47.249827006041485</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>-41.263796760175566</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Before PCA - 5 original indicators</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>0.5014954334092099</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>0.33532724454561325</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>0.07819249554967564</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>-56.55644246615573</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>-43.087874412957405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>After PCA - PC1 + PC2</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>0.4713652325530965</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>0.3734699052481144</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>0.08052085260474846</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>-60.61983671773642</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>-51.64079134893754</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="45" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Statistic</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>N exposed region-year rows</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Overall KMO</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>0.4932114401561532</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>Bartlett chi-square</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>52.124382815326705</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>Bartlett df</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>Bartlett p-value</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="n">
+        <x:v>1.0821794713735653e-7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>KMO Cancer_pct</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="n">
+        <x:v>0.5317306215667762</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="52" t="str">
+        <x:v>KMO Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="B8" s="52" t="n">
+        <x:v>0.5974453404326157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="52" t="str">
+        <x:v>KMO Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="B9" s="52" t="n">
+        <x:v>0.5930552097075041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="52" t="str">
+        <x:v>KMO Disability_pct</x:v>
+      </x:c>
+      <x:c r="B10" s="52" t="n">
+        <x:v>0.3740181505667412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="52" t="str">
+        <x:v>KMO Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="B11" s="52" t="n">
+        <x:v>0.4528779344821376</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="52" t="str">
+        <x:v>PC1 eigenvalue</x:v>
+      </x:c>
+      <x:c r="B12" s="52" t="n">
+        <x:v>2.223645777585634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="52" t="str">
+        <x:v>PC1 explained variance ratio</x:v>
+      </x:c>
+      <x:c r="B13" s="52" t="n">
+        <x:v>0.4312525144408502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="52" t="str">
+        <x:v>PC2 eigenvalue</x:v>
+      </x:c>
+      <x:c r="B14" s="52" t="n">
+        <x:v>1.617062441507156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="52" t="str">
+        <x:v>PC2 explained variance ratio</x:v>
+      </x:c>
+      <x:c r="B15" s="52" t="n">
+        <x:v>0.3136121098680545</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="52" t="str">
+        <x:v>PC3 eigenvalue</x:v>
+      </x:c>
+      <x:c r="B16" s="52" t="n">
+        <x:v>0.7400703623937442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="52" t="str">
+        <x:v>PC3 explained variance ratio</x:v>
+      </x:c>
+      <x:c r="B17" s="52" t="n">
+        <x:v>0.1435287975551504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="52" t="str">
+        <x:v>PC4 eigenvalue</x:v>
+      </x:c>
+      <x:c r="B18" s="52" t="n">
+        <x:v>0.37666349755198236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="52" t="str">
+        <x:v>PC4 explained variance ratio</x:v>
+      </x:c>
+      <x:c r="B19" s="52" t="n">
+        <x:v>0.07304989043432385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="52" t="str">
+        <x:v>PC5 eigenvalue</x:v>
+      </x:c>
+      <x:c r="B20" s="52" t="n">
+        <x:v>0.1988079209614831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="52" t="str">
+        <x:v>PC5 explained variance ratio</x:v>
+      </x:c>
+      <x:c r="B21" s="52" t="n">
+        <x:v>0.03855668770162096</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="52" t="str">
+        <x:v>PC1+PC2 cumulative explained variance</x:v>
+      </x:c>
+      <x:c r="B22" s="52" t="n">
+        <x:v>0.7448646243089048</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>PC1_component_coefficient</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>PC2_component_coefficient</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Cancer_pct</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>-0.4401775476678794</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>-0.49482725658217036</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>0.5269278383595386</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>-0.22804155917001823</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>-0.4731746855545613</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>0.01644828059809269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>Disability_pct</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="n">
+        <x:v>0.18743032291462136</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>0.7182724972329956</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="n">
+        <x:v>0.5191978146075916</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>-0.4323853688767846</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5759,7 +8114,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5775,35 +8130,2697 @@
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="39" t="str">
+    <x:row r="1" ht="44" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Region</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>Year</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Mortality_pct</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>Z_Cancer_pct</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>Z_Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>Z_Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>Z_Disability_pct</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>Z_Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="I1" s="46" t="str">
+        <x:v>PC1</x:v>
+      </x:c>
+      <x:c r="J1" s="46" t="str">
+        <x:v>PC2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>1.1927803741994365</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>-0.6022799713824212</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>3.2145104303134375</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>-0.5014136767974365</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>-0.6034606023823219</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>1.2362678548580095</x:v>
+      </x:c>
+      <x:c r="I2" s="52" t="n">
+        <x:v>2.7249421650343506</x:v>
+      </x:c>
+      <x:c r="J2" s="52" t="n">
+        <x:v>-1.4112581037232659</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>1.1673333046607317</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>-0.3668241776921516</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>2.5733725342121576</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>0.14760067790582168</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>-0.09280910917200139</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>2.0862020050728916</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="n">
+        <x:v>2.5133647699146033</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="n">
+        <x:v>-1.3715989602908336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>1.0989420889081452</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>0.06715316754089584</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>1.5711339839848686</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>0.38620364375159844</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>0.01908471068430512</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>1.2362678548580095</x:v>
+      </x:c>
+      <x:c r="I4" s="52" t="n">
+        <x:v>1.2610177516540708</x:v>
+      </x:c>
+      <x:c r="J4" s="52" t="n">
+        <x:v>-0.9059967847886501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>1.0492775325088857</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>0.6765681629745351</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>0.7273375575067473</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>0.2517215829118755</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>-0.16361880510698676</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I5" s="52" t="n">
+        <x:v>-0.30503145238324647</x:v>
+      </x:c>
+      <x:c r="J5" s="52" t="n">
+        <x:v>-0.4135760094724388</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>1.051190068407256</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>0.796604449953888</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>0.2077947796315715</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>0.43978215404630927</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>-0.18029412599269976</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>0.3863337046431275</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="n">
+        <x:v>-0.2824572927361871</x:v>
+      </x:c>
+      <x:c r="J6" s="52" t="n">
+        <x:v>-0.7308791333194876</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>1.037521695621621</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>0.5611486562636184</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>0.11199256527161</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>0.9268108126252265</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>-0.18271083916454306</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>-0.03863337046431162</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="n">
+        <x:v>-0.6808403669934532</x:v>
+      </x:c>
+      <x:c r="J7" s="52" t="n">
+        <x:v>-0.40249783158536667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B8" s="52" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C8" s="52" t="n">
+        <x:v>1.013552413411938</x:v>
+      </x:c>
+      <x:c r="D8" s="52" t="n">
+        <x:v>1.0228266831072854</x:v>
+      </x:c>
+      <x:c r="E8" s="52" t="n">
+        <x:v>-0.7096956578926744</x:v>
+      </x:c>
+      <x:c r="F8" s="52" t="n">
+        <x:v>1.2636410473446391</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="n">
+        <x:v>-0.20228621585646672</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I8" s="52" t="n">
+        <x:v>-1.7007216041482247</x:v>
+      </x:c>
+      <x:c r="J8" s="52" t="n">
+        <x:v>-0.26834027042604086</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B9" s="52" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C9" s="52" t="n">
+        <x:v>1.0148546155541665</x:v>
+      </x:c>
+      <x:c r="D9" s="52" t="n">
+        <x:v>0.08562028861464047</x:v>
+      </x:c>
+      <x:c r="E9" s="52" t="n">
+        <x:v>-0.4480819186789334</x:v>
+      </x:c>
+      <x:c r="F9" s="52" t="n">
+        <x:v>1.5988639267552103</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="n">
+        <x:v>-0.12301802382003302</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I9" s="52" t="n">
+        <x:v>-1.2940945473982888</x:v>
+      </x:c>
+      <x:c r="J9" s="52" t="n">
+        <x:v>0.19820619585002147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B10" s="52" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C10" s="52" t="n">
+        <x:v>1.028916887976166</x:v>
+      </x:c>
+      <x:c r="D10" s="52" t="n">
+        <x:v>0.5749989970689269</x:v>
+      </x:c>
+      <x:c r="E10" s="52" t="n">
+        <x:v>0.09725376306238516</x:v>
+      </x:c>
+      <x:c r="F10" s="52" t="n">
+        <x:v>1.5813616133922712</x:v>
+      </x:c>
+      <x:c r="G10" s="52" t="n">
+        <x:v>-0.15153523924777454</x:v>
+      </x:c>
+      <x:c r="H10" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I10" s="52" t="n">
+        <x:v>-1.219218854480554</x:v>
+      </x:c>
+      <x:c r="J10" s="52" t="n">
+        <x:v>-0.1890819415201985</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B11" s="52" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C11" s="52" t="n">
+        <x:v>1.1994769264243423</x:v>
+      </x:c>
+      <x:c r="D11" s="52" t="n">
+        <x:v>-1.30864735245323</x:v>
+      </x:c>
+      <x:c r="E11" s="52" t="n">
+        <x:v>-0.4665054214404644</x:v>
+      </x:c>
+      <x:c r="F11" s="52" t="n">
+        <x:v>1.2691774934084257</x:v>
+      </x:c>
+      <x:c r="G11" s="52" t="n">
+        <x:v>-0.3760478929119429</x:v>
+      </x:c>
+      <x:c r="H11" s="52" t="n">
+        <x:v>-0.03863337046431162</x:v>
+      </x:c>
+      <x:c r="I11" s="52" t="n">
+        <x:v>-0.3608613118100059</x:v>
+      </x:c>
+      <x:c r="J11" s="52" t="n">
+        <x:v>0.5214124354729656</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B12" s="52" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C12" s="52" t="n">
+        <x:v>1.369412016597778</x:v>
+      </x:c>
+      <x:c r="D12" s="52" t="n">
+        <x:v>0.385711006063024</x:v>
+      </x:c>
+      <x:c r="E12" s="52" t="n">
+        <x:v>-0.580731138561957</x:v>
+      </x:c>
+      <x:c r="F12" s="52" t="n">
+        <x:v>1.371869638139954</x:v>
+      </x:c>
+      <x:c r="G12" s="52" t="n">
+        <x:v>-0.34656399221546447</x:v>
+      </x:c>
+      <x:c r="H12" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I12" s="52" t="n">
+        <x:v>-1.4305756520800657</x:v>
+      </x:c>
+      <x:c r="J12" s="52" t="n">
+        <x:v>-0.08433792238498919</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B13" s="52" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C13" s="52" t="n">
+        <x:v>1.1347291152233705</x:v>
+      </x:c>
+      <x:c r="D13" s="52" t="n">
+        <x:v>-1.6225884107069246</x:v>
+      </x:c>
+      <x:c r="E13" s="52" t="n">
+        <x:v>0.6610129475652355</x:v>
+      </x:c>
+      <x:c r="F13" s="52" t="n">
+        <x:v>-1.413855707116354</x:v>
+      </x:c>
+      <x:c r="G13" s="52" t="n">
+        <x:v>0.12179502048761222</x:v>
+      </x:c>
+      <x:c r="H13" s="52" t="n">
+        <x:v>1.6612349299654487</x:v>
+      </x:c>
+      <x:c r="I13" s="52" t="n">
+        <x:v>2.6168714659290564</x:v>
+      </x:c>
+      <x:c r="J13" s="52" t="n">
+        <x:v>-0.0019046112260083588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B14" s="52" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C14" s="52" t="n">
+        <x:v>1.148258907235732</x:v>
+      </x:c>
+      <x:c r="D14" s="52" t="n">
+        <x:v>-1.248629208963555</x:v>
+      </x:c>
+      <x:c r="E14" s="52" t="n">
+        <x:v>1.0479065055573873</x:v>
+      </x:c>
+      <x:c r="F14" s="52" t="n">
+        <x:v>-0.9637962206407868</x:v>
+      </x:c>
+      <x:c r="G14" s="52" t="n">
+        <x:v>0.9168936540237927</x:v>
+      </x:c>
+      <x:c r="H14" s="52" t="n">
+        <x:v>0.8113007797505667</x:v>
+      </x:c>
+      <x:c r="I14" s="52" t="n">
+        <x:v>2.1509128920526677</x:v>
+      </x:c>
+      <x:c r="J14" s="52" t="n">
+        <x:v>0.6708216495418926</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B15" s="52" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C15" s="52" t="n">
+        <x:v>1.0527034136913085</x:v>
+      </x:c>
+      <x:c r="D15" s="52" t="n">
+        <x:v>-1.2024614062791883</x:v>
+      </x:c>
+      <x:c r="E15" s="52" t="n">
+        <x:v>0.11936196637622243</x:v>
+      </x:c>
+      <x:c r="F15" s="52" t="n">
+        <x:v>-0.4272967375564204</x:v>
+      </x:c>
+      <x:c r="G15" s="52" t="n">
+        <x:v>1.1764486486796772</x:v>
+      </x:c>
+      <x:c r="H15" s="52" t="n">
+        <x:v>0.3863337046431275</x:v>
+      </x:c>
+      <x:c r="I15" s="52" t="n">
+        <x:v>1.2154634206124268</x:v>
+      </x:c>
+      <x:c r="J15" s="52" t="n">
+        <x:v>1.2387285606209402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B16" s="52" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C16" s="52" t="n">
+        <x:v>0.9942628013708532</x:v>
+      </x:c>
+      <x:c r="D16" s="52" t="n">
+        <x:v>-1.3271144735269773</x:v>
+      </x:c>
+      <x:c r="E16" s="52" t="n">
+        <x:v>-0.07592716289600639</x:v>
+      </x:c>
+      <x:c r="F16" s="52" t="n">
+        <x:v>-1.0461285314603253</x:v>
+      </x:c>
+      <x:c r="G16" s="52" t="n">
+        <x:v>0.917618667975346</x:v>
+      </x:c>
+      <x:c r="H16" s="52" t="n">
+        <x:v>-0.03863337046431162</x:v>
+      </x:c>
+      <x:c r="I16" s="52" t="n">
+        <x:v>1.1910905992725904</x:v>
+      </x:c>
+      <x:c r="J16" s="52" t="n">
+        <x:v>1.3326047033823083</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B17" s="52" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C17" s="52" t="n">
+        <x:v>0.987358874873832</x:v>
+      </x:c>
+      <x:c r="D17" s="52" t="n">
+        <x:v>-0.45915978306088495</x:v>
+      </x:c>
+      <x:c r="E17" s="52" t="n">
+        <x:v>-0.21226108333133623</x:v>
+      </x:c>
+      <x:c r="F17" s="52" t="n">
+        <x:v>-1.4136771120820384</x:v>
+      </x:c>
+      <x:c r="G17" s="52" t="n">
+        <x:v>1.0014786150382804</x:v>
+      </x:c>
+      <x:c r="H17" s="52" t="n">
+        <x:v>1.6612349299654487</x:v>
+      </x:c>
+      <x:c r="I17" s="52" t="n">
+        <x:v>1.8093987818694877</x:v>
+      </x:c>
+      <x:c r="J17" s="52" t="n">
+        <x:v>0.25339743412912785</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B18" s="52" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C18" s="52" t="n">
+        <x:v>0.9863446971064622</x:v>
+      </x:c>
+      <x:c r="D18" s="52" t="n">
+        <x:v>-0.45915978306088495</x:v>
+      </x:c>
+      <x:c r="E18" s="52" t="n">
+        <x:v>-0.4001808114989526</x:v>
+      </x:c>
+      <x:c r="F18" s="52" t="n">
+        <x:v>-1.1541785272213245</x:v>
+      </x:c>
+      <x:c r="G18" s="52" t="n">
+        <x:v>1.1621900409658052</x:v>
+      </x:c>
+      <x:c r="H18" s="52" t="n">
+        <x:v>0.3863337046431275</x:v>
+      </x:c>
+      <x:c r="I18" s="52" t="n">
+        <x:v>0.9557867488574673</x:v>
+      </x:c>
+      <x:c r="J18" s="52" t="n">
+        <x:v>0.96720248130517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B19" s="52" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C19" s="52" t="n">
+        <x:v>0.9583125714612186</x:v>
+      </x:c>
+      <x:c r="D19" s="52" t="n">
+        <x:v>-0.5468786081611822</x:v>
+      </x:c>
+      <x:c r="E19" s="52" t="n">
+        <x:v>-0.4849289242019955</x:v>
+      </x:c>
+      <x:c r="F19" s="52" t="n">
+        <x:v>-0.5496343360626761</x:v>
+      </x:c>
+      <x:c r="G19" s="52" t="n">
+        <x:v>1.392744477559581</x:v>
+      </x:c>
+      <x:c r="H19" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I19" s="52" t="n">
+        <x:v>0.2656163979356725</x:v>
+      </x:c>
+      <x:c r="J19" s="52" t="n">
+        <x:v>1.5729779531098003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B20" s="52" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C20" s="52" t="n">
+        <x:v>0.9623791321782756</x:v>
+      </x:c>
+      <x:c r="D20" s="52" t="n">
+        <x:v>-0.4083752001080821</x:v>
+      </x:c>
+      <x:c r="E20" s="52" t="n">
+        <x:v>-0.5954699407711819</x:v>
+      </x:c>
+      <x:c r="F20" s="52" t="n">
+        <x:v>0.4835379374536556</x:v>
+      </x:c>
+      <x:c r="G20" s="52" t="n">
+        <x:v>1.637557521867224</x:v>
+      </x:c>
+      <x:c r="H20" s="52" t="n">
+        <x:v>-1.3135345957866364</x:v>
+      </x:c>
+      <x:c r="I20" s="52" t="n">
+        <x:v>-0.737866362524067</x:v>
+      </x:c>
+      <x:c r="J20" s="52" t="n">
+        <x:v>2.0899861126589467</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B21" s="52" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C21" s="52" t="n">
+        <x:v>0.9697997580034412</x:v>
+      </x:c>
+      <x:c r="D21" s="52" t="n">
+        <x:v>-0.22370398937061534</x:v>
+      </x:c>
+      <x:c r="E21" s="52" t="n">
+        <x:v>-0.28227039382515423</x:v>
+      </x:c>
+      <x:c r="F21" s="52" t="n">
+        <x:v>0.5126489280471153</x:v>
+      </x:c>
+      <x:c r="G21" s="52" t="n">
+        <x:v>1.8154276113148335</x:v>
+      </x:c>
+      <x:c r="H21" s="52" t="n">
+        <x:v>-2.1634687460015147</x:v>
+      </x:c>
+      <x:c r="I21" s="52" t="n">
+        <x:v>-1.075841211814035</x:v>
+      </x:c>
+      <x:c r="J21" s="52" t="n">
+        <x:v>2.4229203611970997</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B22" s="52" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C22" s="52" t="n">
+        <x:v>1.121446863275139</x:v>
+      </x:c>
+      <x:c r="D22" s="52" t="n">
+        <x:v>-2.2366201864090014</x:v>
+      </x:c>
+      <x:c r="E22" s="52" t="n">
+        <x:v>-0.4554513197835458</x:v>
+      </x:c>
+      <x:c r="F22" s="52" t="n">
+        <x:v>0.33298232352551976</x:v>
+      </x:c>
+      <x:c r="G22" s="52" t="n">
+        <x:v>1.763226606803035</x:v>
+      </x:c>
+      <x:c r="H22" s="52" t="n">
+        <x:v>-1.3135345957866364</x:v>
+      </x:c>
+      <x:c r="I22" s="52" t="n">
+        <x:v>0.23545904381789037</x:v>
+      </x:c>
+      <x:c r="J22" s="52" t="n">
+        <x:v>3.0505097654258044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B23" s="52" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C23" s="52" t="n">
+        <x:v>1.2753481624898797</x:v>
+      </x:c>
+      <x:c r="D23" s="52" t="n">
+        <x:v>-0.6576813346036627</x:v>
+      </x:c>
+      <x:c r="E23" s="52" t="n">
+        <x:v>-0.2749009927205418</x:v>
+      </x:c>
+      <x:c r="F23" s="52" t="n">
+        <x:v>-0.6934033386868153</x:v>
+      </x:c>
+      <x:c r="G23" s="52" t="n">
+        <x:v>1.8434614841082055</x:v>
+      </x:c>
+      <x:c r="H23" s="52" t="n">
+        <x:v>-1.7385016708940757</x:v>
+      </x:c>
+      <x:c r="I23" s="52" t="n">
+        <x:v>-0.08436120907151298</x:v>
+      </x:c>
+      <x:c r="J23" s="52" t="n">
+        <x:v>2.4525325788279213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B24" s="52" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C24" s="52" t="n">
+        <x:v>1.0969896438602886</x:v>
+      </x:c>
+      <x:c r="D24" s="52" t="n">
+        <x:v>-0.9069874690992409</x:v>
+      </x:c>
+      <x:c r="E24" s="52" t="n">
+        <x:v>1.5490257806710315</x:v>
+      </x:c>
+      <x:c r="F24" s="52" t="n">
+        <x:v>-1.405104550434885</x:v>
+      </x:c>
+      <x:c r="G24" s="52" t="n">
+        <x:v>-1.4169262560245055</x:v>
+      </x:c>
+      <x:c r="H24" s="52" t="n">
+        <x:v>1.6612349299654487</x:v>
+      </x:c>
+      <x:c r="I24" s="52" t="n">
+        <x:v>2.4772548293840693</x:v>
+      </x:c>
+      <x:c r="J24" s="52" t="n">
+        <x:v>-1.6635845253390333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B25" s="52" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C25" s="52" t="n">
+        <x:v>1.083291954810638</x:v>
+      </x:c>
+      <x:c r="D25" s="52" t="n">
+        <x:v>0.8012212302223242</x:v>
+      </x:c>
+      <x:c r="E25" s="52" t="n">
+        <x:v>-0.042764857925250484</x:v>
+      </x:c>
+      <x:c r="F25" s="52" t="n">
+        <x:v>-1.2977689348111483</x:v>
+      </x:c>
+      <x:c r="G25" s="52" t="n">
+        <x:v>-0.6544532503081978</x:v>
+      </x:c>
+      <x:c r="H25" s="52" t="n">
+        <x:v>1.2362678548580095</x:v>
+      </x:c>
+      <x:c r="I25" s="52" t="n">
+        <x:v>0.7580610017228369</x:v>
+      </x:c>
+      <x:c r="J25" s="52" t="n">
+        <x:v>-1.412679908853019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B26" s="52" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C26" s="52" t="n">
+        <x:v>1.012812316054036</x:v>
+      </x:c>
+      <x:c r="D26" s="52" t="n">
+        <x:v>0.8196883512960714</x:v>
+      </x:c>
+      <x:c r="E26" s="52" t="n">
+        <x:v>-0.17541407780827412</x:v>
+      </x:c>
+      <x:c r="F26" s="52" t="n">
+        <x:v>-1.3493828997283859</x:v>
+      </x:c>
+      <x:c r="G26" s="52" t="n">
+        <x:v>-0.5188756413678343</x:v>
+      </x:c>
+      <x:c r="H26" s="52" t="n">
+        <x:v>0.3863337046431275</x:v>
+      </x:c>
+      <x:c r="I26" s="52" t="n">
+        <x:v>0.2885854462547637</x:v>
+      </x:c>
+      <x:c r="J26" s="52" t="n">
+        <x:v>-0.9275366109597278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B27" s="52" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C27" s="52" t="n">
+        <x:v>1.0025049341624674</x:v>
+      </x:c>
+      <x:c r="D27" s="52" t="n">
+        <x:v>0.8981736158594937</x:v>
+      </x:c>
+      <x:c r="E27" s="52" t="n">
+        <x:v>-0.3154326987959102</x:v>
+      </x:c>
+      <x:c r="F27" s="52" t="n">
+        <x:v>-1.2774091008991582</x:v>
+      </x:c>
+      <x:c r="G27" s="52" t="n">
+        <x:v>-0.9451838448808508</x:v>
+      </x:c>
+      <x:c r="H27" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I27" s="52" t="n">
+        <x:v>-0.37498493154263757</x:v>
+      </x:c>
+      <x:c r="J27" s="52" t="n">
+        <x:v>-0.8719657160906301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B28" s="52" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C28" s="52" t="n">
+        <x:v>0.97553166012387</x:v>
+      </x:c>
+      <x:c r="D28" s="52" t="n">
+        <x:v>0.602699678679549</x:v>
+      </x:c>
+      <x:c r="E28" s="52" t="n">
+        <x:v>-0.8312907761187794</x:v>
+      </x:c>
+      <x:c r="F28" s="52" t="n">
+        <x:v>-0.6917959833779738</x:v>
+      </x:c>
+      <x:c r="G28" s="52" t="n">
+        <x:v>-1.0174435687189416</x:v>
+      </x:c>
+      <x:c r="H28" s="52" t="n">
+        <x:v>-0.03863337046431162</x:v>
+      </x:c>
+      <x:c r="I28" s="52" t="n">
+        <x:v>-0.5867429094954862</x:v>
+      </x:c>
+      <x:c r="J28" s="52" t="n">
+        <x:v>-0.8341394670436502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B29" s="52" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C29" s="52" t="n">
+        <x:v>0.9692931924059508</x:v>
+      </x:c>
+      <x:c r="D29" s="52" t="n">
+        <x:v>1.2213482346500606</x:v>
+      </x:c>
+      <x:c r="E29" s="52" t="n">
+        <x:v>-0.4480819186789334</x:v>
+      </x:c>
+      <x:c r="F29" s="52" t="n">
+        <x:v>-0.4276539276250517</x:v>
+      </x:c>
+      <x:c r="G29" s="52" t="n">
+        <x:v>-1.1245039622315636</x:v>
+      </x:c>
+      <x:c r="H29" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I29" s="52" t="n">
+        <x:v>-1.02282837381588</x:v>
+      </x:c>
+      <x:c r="J29" s="52" t="n">
+        <x:v>-1.1164554881428608</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B30" s="52" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C30" s="52" t="n">
+        <x:v>0.9577101612387616</x:v>
+      </x:c>
+      <x:c r="D30" s="52" t="n">
+        <x:v>1.5075886112931356</x:v>
+      </x:c>
+      <x:c r="E30" s="52" t="n">
+        <x:v>-0.5659923363527322</x:v>
+      </x:c>
+      <x:c r="F30" s="52" t="n">
+        <x:v>0.03419283111535158</x:v>
+      </x:c>
+      <x:c r="G30" s="52" t="n">
+        <x:v>-1.2214141604224482</x:v>
+      </x:c>
+      <x:c r="H30" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I30" s="52" t="n">
+        <x:v>-1.4476533469371053</x:v>
+      </x:c>
+      <x:c r="J30" s="52" t="n">
+        <x:v>-1.293217897932309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B31" s="52" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C31" s="52" t="n">
+        <x:v>0.9717110858523637</x:v>
+      </x:c>
+      <x:c r="D31" s="52" t="n">
+        <x:v>0.5888493378742379</x:v>
+      </x:c>
+      <x:c r="E31" s="52" t="n">
+        <x:v>-1.3471488534416483</x:v>
+      </x:c>
+      <x:c r="F31" s="52" t="n">
+        <x:v>0.4629995085073502</x:v>
+      </x:c>
+      <x:c r="G31" s="52" t="n">
+        <x:v>-1.1269206754034058</x:v>
+      </x:c>
+      <x:c r="H31" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I31" s="52" t="n">
+        <x:v>-1.6400475819157414</x:v>
+      </x:c>
+      <x:c r="J31" s="52" t="n">
+        <x:v>-0.5855393096304059</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B32" s="52" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C32" s="52" t="n">
+        <x:v>0.9764503159103964</x:v>
+      </x:c>
+      <x:c r="D32" s="52" t="n">
+        <x:v>1.987733759210547</x:v>
+      </x:c>
+      <x:c r="E32" s="52" t="n">
+        <x:v>-0.9160388888218218</x:v>
+      </x:c>
+      <x:c r="F32" s="52" t="n">
+        <x:v>0.8546584187616831</x:v>
+      </x:c>
+      <x:c r="G32" s="52" t="n">
+        <x:v>-1.0991284739272174</x:v>
+      </x:c>
+      <x:c r="H32" s="52" t="n">
+        <x:v>-0.8885675206791936</x:v>
+      </x:c>
+      <x:c r="I32" s="52" t="n">
+        <x:v>-2.4293972113009854</x:v>
+      </x:c>
+      <x:c r="J32" s="52" t="n">
+        <x:v>-1.1659024034780958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B33" s="52" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C33" s="52" t="n">
+        <x:v>1.1551925165753971</x:v>
+      </x:c>
+      <x:c r="D33" s="52" t="n">
+        <x:v>-0.5653457292349294</x:v>
+      </x:c>
+      <x:c r="E33" s="52" t="n">
+        <x:v>-1.3213559495755047</x:v>
+      </x:c>
+      <x:c r="F33" s="52" t="n">
+        <x:v>1.204526090986142</x:v>
+      </x:c>
+      <x:c r="G33" s="52" t="n">
+        <x:v>-1.1102453545176927</x:v>
+      </x:c>
+      <x:c r="H33" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I33" s="52" t="n">
+        <x:v>-1.466151975382498</x:v>
+      </x:c>
+      <x:c r="J33" s="52" t="n">
+        <x:v>0.0038802766490379937</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B34" s="52" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C34" s="52" t="n">
+        <x:v>1.3669555213498588</x:v>
+      </x:c>
+      <x:c r="D34" s="52" t="n">
+        <x:v>1.5445228534406275</x:v>
+      </x:c>
+      <x:c r="E34" s="52" t="n">
+        <x:v>-0.9307776910310467</x:v>
+      </x:c>
+      <x:c r="F34" s="52" t="n">
+        <x:v>1.4899209558226327</x:v>
+      </x:c>
+      <x:c r="G34" s="52" t="n">
+        <x:v>-1.1104870258348776</x:v>
+      </x:c>
+      <x:c r="H34" s="52" t="n">
+        <x:v>-0.4636004455717545</x:v>
+      </x:c>
+      <x:c r="I34" s="52" t="n">
+        <x:v>-2.3241491184819782</x:v>
+      </x:c>
+      <x:c r="J34" s="52" t="n">
+        <x:v>-1.1246876119640266</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="44" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>Term</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Coefficient</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>HC3_SE</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>t</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>p_value</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>CI95_low</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>CI95_high</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Baseline</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="str">
+        <x:v>Intercept</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>1.1112052658427691</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>0.03646937228173757</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>30.469547357666396</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>6.60025012208904e-204</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>1.03972660963178</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>1.1826839220537582</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>Baseline</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="str">
+        <x:v>Year_centered</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>0.007267977265287559</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>0.008810454644144821</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>0.8249264718839057</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>0.40941333630641963</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>-0.010000196524659949</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>0.024536151055235066</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>Baseline</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="str">
+        <x:v>Region_Karaganda</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>-0.05748305703281368</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>0.050354611749657295</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>-1.141564894166916</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>0.25363492329549275</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>-0.1561762825176394</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>0.04121016845201205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>Baseline</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="str">
+        <x:v>Region_Pavlodar</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>-0.059528601993312225</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>0.05351893180340928</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>-1.1122905481742091</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>0.2660132464579924</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>-0.1644237808190497</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>0.04536657683242526</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="str">
+        <x:v>Intercept</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>0.5962971428951234</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>1.853581084744568</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>0.32170005822933606</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>0.7476799337314686</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>-3.0366550256289155</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>4.229249311419163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="str">
+        <x:v>Cancer_pct</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>-1.1974040665895127</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>1.6812004410504504</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>-0.7122315919934857</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>0.476321376961942</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>-4.492496381841249</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>2.0976882486622244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B8" s="52" t="str">
+        <x:v>Infant_mortality_pct</x:v>
+      </x:c>
+      <x:c r="C8" s="52" t="n">
+        <x:v>0.30052569129941376</x:v>
+      </x:c>
+      <x:c r="D8" s="52" t="n">
+        <x:v>0.1574779671167105</x:v>
+      </x:c>
+      <x:c r="E8" s="52" t="n">
+        <x:v>1.9083665912240748</x:v>
+      </x:c>
+      <x:c r="F8" s="52" t="n">
+        <x:v>0.05634385171485081</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="n">
+        <x:v>-0.008125452607921746</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="n">
+        <x:v>0.6091768352067493</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B9" s="52" t="str">
+        <x:v>Circulatory_pct</x:v>
+      </x:c>
+      <x:c r="C9" s="52" t="n">
+        <x:v>-0.039372808645952675</x:v>
+      </x:c>
+      <x:c r="D9" s="52" t="n">
+        <x:v>0.12015471246096283</x:v>
+      </x:c>
+      <x:c r="E9" s="52" t="n">
+        <x:v>-0.3276842650573904</x:v>
+      </x:c>
+      <x:c r="F9" s="52" t="n">
+        <x:v>0.743150401761731</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="n">
+        <x:v>-0.27487171764220586</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="n">
+        <x:v>0.19612610035030054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B10" s="52" t="str">
+        <x:v>Disability_pct</x:v>
+      </x:c>
+      <x:c r="C10" s="52" t="n">
+        <x:v>-0.09148597434370909</x:v>
+      </x:c>
+      <x:c r="D10" s="52" t="n">
+        <x:v>0.18039365611428151</x:v>
+      </x:c>
+      <x:c r="E10" s="52" t="n">
+        <x:v>-0.5071462950213262</x:v>
+      </x:c>
+      <x:c r="F10" s="52" t="n">
+        <x:v>0.6120521739910052</x:v>
+      </x:c>
+      <x:c r="G10" s="52" t="n">
+        <x:v>-0.4450510433672046</x:v>
+      </x:c>
+      <x:c r="H10" s="52" t="n">
+        <x:v>0.2620790946797864</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B11" s="52" t="str">
+        <x:v>Unemployment_pct</x:v>
+      </x:c>
+      <x:c r="C11" s="52" t="n">
+        <x:v>0.2066478871956345</x:v>
+      </x:c>
+      <x:c r="D11" s="52" t="n">
+        <x:v>0.2287843513409191</x:v>
+      </x:c>
+      <x:c r="E11" s="52" t="n">
+        <x:v>0.9032431020061407</x:v>
+      </x:c>
+      <x:c r="F11" s="52" t="n">
+        <x:v>0.36639688679490146</x:v>
+      </x:c>
+      <x:c r="G11" s="52" t="n">
+        <x:v>-0.24176120165892492</x:v>
+      </x:c>
+      <x:c r="H11" s="52" t="n">
+        <x:v>0.655056976050194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B12" s="52" t="str">
+        <x:v>Year_centered</x:v>
+      </x:c>
+      <x:c r="C12" s="52" t="n">
+        <x:v>0.045273611829332795</x:v>
+      </x:c>
+      <x:c r="D12" s="52" t="n">
+        <x:v>0.024736979359024094</x:v>
+      </x:c>
+      <x:c r="E12" s="52" t="n">
+        <x:v>1.8301996849432185</x:v>
+      </x:c>
+      <x:c r="F12" s="52" t="n">
+        <x:v>0.06722008490072849</x:v>
+      </x:c>
+      <x:c r="G12" s="52" t="n">
+        <x:v>-0.0032099768006651416</x:v>
+      </x:c>
+      <x:c r="H12" s="52" t="n">
+        <x:v>0.09375720045933073</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B13" s="52" t="str">
+        <x:v>Region_Karaganda</x:v>
+      </x:c>
+      <x:c r="C13" s="52" t="n">
+        <x:v>0.013368603211869775</x:v>
+      </x:c>
+      <x:c r="D13" s="52" t="n">
+        <x:v>0.18461671216829595</x:v>
+      </x:c>
+      <x:c r="E13" s="52" t="n">
+        <x:v>0.0724127466839676</x:v>
+      </x:c>
+      <x:c r="F13" s="52" t="n">
+        <x:v>0.9422734410390985</x:v>
+      </x:c>
+      <x:c r="G13" s="52" t="n">
+        <x:v>-0.3484735035821878</x:v>
+      </x:c>
+      <x:c r="H13" s="52" t="n">
+        <x:v>0.3752107100059274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="52" t="str">
+        <x:v>Before PCA</x:v>
+      </x:c>
+      <x:c r="B14" s="52" t="str">
+        <x:v>Region_Pavlodar</x:v>
+      </x:c>
+      <x:c r="C14" s="52" t="n">
+        <x:v>0.002434164326982808</x:v>
+      </x:c>
+      <x:c r="D14" s="52" t="n">
+        <x:v>0.1270245229042833</x:v>
+      </x:c>
+      <x:c r="E14" s="52" t="n">
+        <x:v>0.019162947998765736</x:v>
+      </x:c>
+      <x:c r="F14" s="52" t="n">
+        <x:v>0.9847111153851159</x:v>
+      </x:c>
+      <x:c r="G14" s="52" t="n">
+        <x:v>-0.2465293257187956</x:v>
+      </x:c>
+      <x:c r="H14" s="52" t="n">
+        <x:v>0.25139765437276124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="52" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B15" s="52" t="str">
+        <x:v>Intercept</x:v>
+      </x:c>
+      <x:c r="C15" s="52" t="n">
+        <x:v>1.1009488070660316</x:v>
+      </x:c>
+      <x:c r="D15" s="52" t="n">
+        <x:v>0.036148736611073956</x:v>
+      </x:c>
+      <x:c r="E15" s="52" t="n">
+        <x:v>30.456079804702284</x:v>
+      </x:c>
+      <x:c r="F15" s="52" t="n">
+        <x:v>9.952345493268548e-204</x:v>
+      </x:c>
+      <x:c r="G15" s="52" t="n">
+        <x:v>1.0300985852217022</x:v>
+      </x:c>
+      <x:c r="H15" s="52" t="n">
+        <x:v>1.171799028910361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="52" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B16" s="52" t="str">
+        <x:v>PC1</x:v>
+      </x:c>
+      <x:c r="C16" s="52" t="n">
+        <x:v>0.0958213743627061</x:v>
+      </x:c>
+      <x:c r="D16" s="52" t="n">
+        <x:v>0.018526411080166005</x:v>
+      </x:c>
+      <x:c r="E16" s="52" t="n">
+        <x:v>5.172149853961218</x:v>
+      </x:c>
+      <x:c r="F16" s="52" t="n">
+        <x:v>2.3141587187687722e-7</x:v>
+      </x:c>
+      <x:c r="G16" s="52" t="n">
+        <x:v>0.059510275882796934</x:v>
+      </x:c>
+      <x:c r="H16" s="52" t="n">
+        <x:v>0.13213247284261526</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="52" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B17" s="52" t="str">
+        <x:v>PC2</x:v>
+      </x:c>
+      <x:c r="C17" s="52" t="n">
+        <x:v>-0.03697792604899301</x:v>
+      </x:c>
+      <x:c r="D17" s="52" t="n">
+        <x:v>0.06728590099583476</x:v>
+      </x:c>
+      <x:c r="E17" s="52" t="n">
+        <x:v>-0.5495642549437226</x:v>
+      </x:c>
+      <x:c r="F17" s="52" t="n">
+        <x:v>0.5826182815627254</x:v>
+      </x:c>
+      <x:c r="G17" s="52" t="n">
+        <x:v>-0.16885586866815688</x:v>
+      </x:c>
+      <x:c r="H17" s="52" t="n">
+        <x:v>0.09490001657017087</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="52" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B18" s="52" t="str">
+        <x:v>Year_centered</x:v>
+      </x:c>
+      <x:c r="C18" s="52" t="n">
+        <x:v>0.048452430451004544</x:v>
+      </x:c>
+      <x:c r="D18" s="52" t="n">
+        <x:v>0.019350270690179347</x:v>
+      </x:c>
+      <x:c r="E18" s="52" t="n">
+        <x:v>2.5039665453153135</x:v>
+      </x:c>
+      <x:c r="F18" s="52" t="n">
+        <x:v>0.0122809645967392</x:v>
+      </x:c>
+      <x:c r="G18" s="52" t="n">
+        <x:v>0.010526596807152011</x:v>
+      </x:c>
+      <x:c r="H18" s="52" t="n">
+        <x:v>0.08637826409485708</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="52" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B19" s="52" t="str">
+        <x:v>Region_Karaganda</x:v>
+      </x:c>
+      <x:c r="C19" s="52" t="n">
+        <x:v>-0.06768746669774067</x:v>
+      </x:c>
+      <x:c r="D19" s="52" t="n">
+        <x:v>0.14096394063020165</x:v>
+      </x:c>
+      <x:c r="E19" s="52" t="n">
+        <x:v>-0.4801757555523286</x:v>
+      </x:c>
+      <x:c r="F19" s="52" t="n">
+        <x:v>0.6311024246726579</x:v>
+      </x:c>
+      <x:c r="G19" s="52" t="n">
+        <x:v>-0.3439717134517783</x:v>
+      </x:c>
+      <x:c r="H19" s="52" t="n">
+        <x:v>0.20859678005629695</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="52" t="str">
+        <x:v>After PCA</x:v>
+      </x:c>
+      <x:c r="B20" s="52" t="str">
+        <x:v>Region_Pavlodar</x:v>
+      </x:c>
+      <x:c r="C20" s="52" t="n">
+        <x:v>-0.01855481599816793</x:v>
+      </x:c>
+      <x:c r="D20" s="52" t="n">
+        <x:v>0.03869941443574945</x:v>
+      </x:c>
+      <x:c r="E20" s="52" t="n">
+        <x:v>-0.4794598644114755</x:v>
+      </x:c>
+      <x:c r="F20" s="52" t="n">
+        <x:v>0.631611514349288</x:v>
+      </x:c>
+      <x:c r="G20" s="52" t="n">
+        <x:v>-0.09440427451502631</x:v>
+      </x:c>
+      <x:c r="H20" s="52" t="n">
+        <x:v>0.05729464251869046</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="44" customHeight="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>Region</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>Year</x:v>
+      </x:c>
+      <x:c r="C1" s="46" t="str">
+        <x:v>Observed_Mortality</x:v>
+      </x:c>
+      <x:c r="D1" s="46" t="str">
+        <x:v>Fitted_Baseline</x:v>
+      </x:c>
+      <x:c r="E1" s="46" t="str">
+        <x:v>Residual_Baseline</x:v>
+      </x:c>
+      <x:c r="F1" s="46" t="str">
+        <x:v>Fitted_Before_PCA</x:v>
+      </x:c>
+      <x:c r="G1" s="46" t="str">
+        <x:v>Residual_Before_PCA</x:v>
+      </x:c>
+      <x:c r="H1" s="46" t="str">
+        <x:v>Fitted_After_PCA</x:v>
+      </x:c>
+      <x:c r="I1" s="46" t="str">
+        <x:v>Residual_After_PCA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B2" s="52" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C2" s="52" t="n">
+        <x:v>1.1927803741994365</x:v>
+      </x:c>
+      <x:c r="D2" s="52" t="n">
+        <x:v>1.0748653795163314</x:v>
+      </x:c>
+      <x:c r="E2" s="52" t="n">
+        <x:v>0.11791499468310507</x:v>
+      </x:c>
+      <x:c r="F2" s="52" t="n">
+        <x:v>1.2123773722403453</x:v>
+      </x:c>
+      <x:c r="G2" s="52" t="n">
+        <x:v>-0.019596998040908753</x:v>
+      </x:c>
+      <x:c r="H2" s="52" t="n">
+        <x:v>1.1719797559190095</x:v>
+      </x:c>
+      <x:c r="I2" s="52" t="n">
+        <x:v>0.020800618280427008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B3" s="52" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C3" s="52" t="n">
+        <x:v>1.1673333046607317</x:v>
+      </x:c>
+      <x:c r="D3" s="52" t="n">
+        <x:v>1.082133356781619</x:v>
+      </x:c>
+      <x:c r="E3" s="52" t="n">
+        <x:v>0.08519994787911278</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="n">
+        <x:v>1.2069432654423353</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="n">
+        <x:v>-0.039609960781603615</x:v>
+      </x:c>
+      <x:c r="H3" s="52" t="n">
+        <x:v>1.1986920367125475</x:v>
+      </x:c>
+      <x:c r="I3" s="52" t="n">
+        <x:v>-0.03135873205181583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B4" s="52" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C4" s="52" t="n">
+        <x:v>1.0989420889081452</x:v>
+      </x:c>
+      <x:c r="D4" s="52" t="n">
+        <x:v>1.0894013340469064</x:v>
+      </x:c>
+      <x:c r="E4" s="52" t="n">
+        <x:v>0.009540754861238732</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="n">
+        <x:v>1.1083927057259464</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="n">
+        <x:v>-0.009450616817801238</x:v>
+      </x:c>
+      <x:c r="H4" s="52" t="n">
+        <x:v>1.1099258518808208</x:v>
+      </x:c>
+      <x:c r="I4" s="52" t="n">
+        <x:v>-0.01098376297267567</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B5" s="52" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C5" s="52" t="n">
+        <x:v>1.0492775325088857</x:v>
+      </x:c>
+      <x:c r="D5" s="52" t="n">
+        <x:v>1.096669311312194</x:v>
+      </x:c>
+      <x:c r="E5" s="52" t="n">
+        <x:v>-0.04739177880330825</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="n">
+        <x:v>0.9962621578419024</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="n">
+        <x:v>0.05301537466698325</x:v>
+      </x:c>
+      <x:c r="H5" s="52" t="n">
+        <x:v>0.9901085962667169</x:v>
+      </x:c>
+      <x:c r="I5" s="52" t="n">
+        <x:v>0.05916893624216879</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B6" s="52" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C6" s="52" t="n">
+        <x:v>1.051190068407256</x:v>
+      </x:c>
+      <x:c r="D6" s="52" t="n">
+        <x:v>1.1039372885774816</x:v>
+      </x:c>
+      <x:c r="E6" s="52" t="n">
+        <x:v>-0.052747220170225706</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="n">
+        <x:v>1.033863270536565</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="n">
+        <x:v>0.017326797870691024</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:v>1.0524573251689164</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="n">
+        <x:v>-0.0012672567616605068</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B7" s="52" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="n">
+        <x:v>1.037521695621621</x:v>
+      </x:c>
+      <x:c r="D7" s="52" t="n">
+        <x:v>1.1112052658427691</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="n">
+        <x:v>-0.07368357022114802</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="n">
+        <x:v>1.0461197074687485</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="n">
+        <x:v>-0.008598011847127385</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:v>1.0505932824303534</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="n">
+        <x:v>-0.013071586808732327</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B8" s="52" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C8" s="52" t="n">
+        <x:v>1.013552413411938</x:v>
+      </x:c>
+      <x:c r="D8" s="52" t="n">
+        <x:v>1.1184732431080566</x:v>
+      </x:c>
+      <x:c r="E8" s="52" t="n">
+        <x:v>-0.1049208296961186</x:v>
+      </x:c>
+      <x:c r="F8" s="52" t="n">
+        <x:v>0.9850525854344108</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="n">
+        <x:v>0.02849982797752726</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="n">
+        <x:v>0.9963584226749881</x:v>
+      </x:c>
+      <x:c r="I8" s="52" t="n">
+        <x:v>0.017193990736949938</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B9" s="52" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C9" s="52" t="n">
+        <x:v>1.0148546155541665</x:v>
+      </x:c>
+      <x:c r="D9" s="52" t="n">
+        <x:v>1.1257412203733443</x:v>
+      </x:c>
+      <x:c r="E9" s="52" t="n">
+        <x:v>-0.11088660481917789</x:v>
+      </x:c>
+      <x:c r="F9" s="52" t="n">
+        <x:v>1.06557980775645</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="n">
+        <x:v>-0.05072519220228355</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="n">
+        <x:v>1.0665224958284583</x:v>
+      </x:c>
+      <x:c r="I9" s="52" t="n">
+        <x:v>-0.05166788027429181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B10" s="52" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C10" s="52" t="n">
+        <x:v>1.028916887976166</x:v>
+      </x:c>
+      <x:c r="D10" s="52" t="n">
+        <x:v>1.1330091976386318</x:v>
+      </x:c>
+      <x:c r="E10" s="52" t="n">
+        <x:v>-0.10409230966246574</x:v>
+      </x:c>
+      <x:c r="F10" s="52" t="n">
+        <x:v>1.1441041268142333</x:v>
+      </x:c>
+      <x:c r="G10" s="52" t="n">
+        <x:v>-0.11518723883806725</x:v>
+      </x:c>
+      <x:c r="H10" s="52" t="n">
+        <x:v>1.1364707301845283</x:v>
+      </x:c>
+      <x:c r="I10" s="52" t="n">
+        <x:v>-0.10755384220836217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B11" s="52" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C11" s="52" t="n">
+        <x:v>1.1994769264243423</x:v>
+      </x:c>
+      <x:c r="D11" s="52" t="n">
+        <x:v>1.1402771749039193</x:v>
+      </x:c>
+      <x:c r="E11" s="52" t="n">
+        <x:v>0.059199751520423005</x:v>
+      </x:c>
+      <x:c r="F11" s="52" t="n">
+        <x:v>1.2282975964790146</x:v>
+      </x:c>
+      <x:c r="G11" s="52" t="n">
+        <x:v>-0.02882067005467226</x:v>
+      </x:c>
+      <x:c r="H11" s="52" t="n">
+        <x:v>1.2408995515381414</x:v>
+      </x:c>
+      <x:c r="I11" s="52" t="n">
+        <x:v>-0.041422625113799016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="52" t="str">
+        <x:v>East Kazakhstan+Abay</x:v>
+      </x:c>
+      <x:c r="B12" s="52" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C12" s="52" t="n">
+        <x:v>1.369412016597778</x:v>
+      </x:c>
+      <x:c r="D12" s="52" t="n">
+        <x:v>1.1475451521692068</x:v>
+      </x:c>
+      <x:c r="E12" s="52" t="n">
+        <x:v>0.22186686442857106</x:v>
+      </x:c>
+      <x:c r="F12" s="52" t="n">
+        <x:v>1.1962653285305316</x:v>
+      </x:c>
+      <x:c r="G12" s="52" t="n">
+        <x:v>0.1731466880672463</x:v>
+      </x:c>
+      <x:c r="H12" s="52" t="n">
+        <x:v>1.2092498756659957</x:v>
+      </x:c>
+      <x:c r="I12" s="52" t="n">
+        <x:v>0.16016214093178216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B13" s="52" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C13" s="52" t="n">
+        <x:v>1.1347291152233705</x:v>
+      </x:c>
+      <x:c r="D13" s="52" t="n">
+        <x:v>1.0173823224835177</x:v>
+      </x:c>
+      <x:c r="E13" s="52" t="n">
+        <x:v>0.11734679273985282</x:v>
+      </x:c>
+      <x:c r="F13" s="52" t="n">
+        <x:v>1.057269717009583</x:v>
+      </x:c>
+      <x:c r="G13" s="52" t="n">
+        <x:v>0.07745939821378744</x:v>
+      </x:c>
+      <x:c r="H13" s="52" t="n">
+        <x:v>1.0418218370822072</x:v>
+      </x:c>
+      <x:c r="I13" s="52" t="n">
+        <x:v>0.09290727814116329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B14" s="52" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C14" s="52" t="n">
+        <x:v>1.148258907235732</x:v>
+      </x:c>
+      <x:c r="D14" s="52" t="n">
+        <x:v>1.0246502997488052</x:v>
+      </x:c>
+      <x:c r="E14" s="52" t="n">
+        <x:v>0.12360860748692692</x:v>
+      </x:c>
+      <x:c r="F14" s="52" t="n">
+        <x:v>1.0430491427089918</x:v>
+      </x:c>
+      <x:c r="G14" s="52" t="n">
+        <x:v>0.10520976452674025</x:v>
+      </x:c>
+      <x:c r="H14" s="52" t="n">
+        <x:v>1.0207494546663987</x:v>
+      </x:c>
+      <x:c r="I14" s="52" t="n">
+        <x:v>0.12750945256933344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B15" s="52" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C15" s="52" t="n">
+        <x:v>1.0527034136913085</x:v>
+      </x:c>
+      <x:c r="D15" s="52" t="n">
+        <x:v>1.0319182770140927</x:v>
+      </x:c>
+      <x:c r="E15" s="52" t="n">
+        <x:v>0.02078513667721582</x:v>
+      </x:c>
+      <x:c r="F15" s="52" t="n">
+        <x:v>0.9690749021829608</x:v>
+      </x:c>
+      <x:c r="G15" s="52" t="n">
+        <x:v>0.08362851150834771</x:v>
+      </x:c>
+      <x:c r="H15" s="52" t="n">
+        <x:v>0.9585658113565392</x:v>
+      </x:c>
+      <x:c r="I15" s="52" t="n">
+        <x:v>0.09413760233476931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B16" s="52" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C16" s="52" t="n">
+        <x:v>0.9942628013708532</x:v>
+      </x:c>
+      <x:c r="D16" s="52" t="n">
+        <x:v>1.0391862542793802</x:v>
+      </x:c>
+      <x:c r="E16" s="52" t="n">
+        <x:v>-0.04492345290852695</x:v>
+      </x:c>
+      <x:c r="F16" s="52" t="n">
+        <x:v>1.0044296806816868</x:v>
+      </x:c>
+      <x:c r="G16" s="52" t="n">
+        <x:v>-0.010166879310833599</x:v>
+      </x:c>
+      <x:c r="H16" s="52" t="n">
+        <x:v>1.0012114595048693</x:v>
+      </x:c>
+      <x:c r="I16" s="52" t="n">
+        <x:v>-0.006948658134016128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B17" s="52" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C17" s="52" t="n">
+        <x:v>0.987358874873832</x:v>
+      </x:c>
+      <x:c r="D17" s="52" t="n">
+        <x:v>1.0464542315446679</x:v>
+      </x:c>
+      <x:c r="E17" s="52" t="n">
+        <x:v>-0.059095356670835875</x:v>
+      </x:c>
+      <x:c r="F17" s="52" t="n">
+        <x:v>1.1036601610689227</x:v>
+      </x:c>
+      <x:c r="G17" s="52" t="n">
+        <x:v>-0.11630128619509073</x:v>
+      </x:c>
+      <x:c r="H17" s="52" t="n">
+        <x:v>1.1488178763859955</x:v>
+      </x:c>
+      <x:c r="I17" s="52" t="n">
+        <x:v>-0.16145900151216352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B18" s="52" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C18" s="52" t="n">
+        <x:v>0.9863446971064622</x:v>
+      </x:c>
+      <x:c r="D18" s="52" t="n">
+        <x:v>1.0537222088099554</x:v>
+      </x:c>
+      <x:c r="E18" s="52" t="n">
+        <x:v>-0.06737751170349315</x:v>
+      </x:c>
+      <x:c r="F18" s="52" t="n">
+        <x:v>1.0598079100931814</x:v>
+      </x:c>
+      <x:c r="G18" s="52" t="n">
+        <x:v>-0.0734632129867192</x:v>
+      </x:c>
+      <x:c r="H18" s="52" t="n">
+        <x:v>1.089080998413371</x:v>
+      </x:c>
+      <x:c r="I18" s="52" t="n">
+        <x:v>-0.1027363013069087</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B19" s="52" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C19" s="52" t="n">
+        <x:v>0.9583125714612186</x:v>
+      </x:c>
+      <x:c r="D19" s="52" t="n">
+        <x:v>1.0609901860752429</x:v>
+      </x:c>
+      <x:c r="E19" s="52" t="n">
+        <x:v>-0.10267761461402425</x:v>
+      </x:c>
+      <x:c r="F19" s="52" t="n">
+        <x:v>1.037059463630976</x:v>
+      </x:c>
+      <x:c r="G19" s="52" t="n">
+        <x:v>-0.07874689216975739</x:v>
+      </x:c>
+      <x:c r="H19" s="52" t="n">
+        <x:v>1.0490000366959724</x:v>
+      </x:c>
+      <x:c r="I19" s="52" t="n">
+        <x:v>-0.0906874652347538</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B20" s="52" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C20" s="52" t="n">
+        <x:v>0.9623791321782756</x:v>
+      </x:c>
+      <x:c r="D20" s="52" t="n">
+        <x:v>1.0682581633405306</x:v>
+      </x:c>
+      <x:c r="E20" s="52" t="n">
+        <x:v>-0.10587903116225494</x:v>
+      </x:c>
+      <x:c r="F20" s="52" t="n">
+        <x:v>0.9963508160797295</x:v>
+      </x:c>
+      <x:c r="G20" s="52" t="n">
+        <x:v>-0.033971683901453886</x:v>
+      </x:c>
+      <x:c r="H20" s="52" t="n">
+        <x:v>0.9821794803999082</x:v>
+      </x:c>
+      <x:c r="I20" s="52" t="n">
+        <x:v>-0.01980034822163257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B21" s="52" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C21" s="52" t="n">
+        <x:v>0.9697997580034412</x:v>
+      </x:c>
+      <x:c r="D21" s="52" t="n">
+        <x:v>1.075526140605818</x:v>
+      </x:c>
+      <x:c r="E21" s="52" t="n">
+        <x:v>-0.10572638260237688</x:v>
+      </x:c>
+      <x:c r="F21" s="52" t="n">
+        <x:v>1.0136747734714016</x:v>
+      </x:c>
+      <x:c r="G21" s="52" t="n">
+        <x:v>-0.043875015467960354</x:v>
+      </x:c>
+      <x:c r="H21" s="52" t="n">
+        <x:v>0.9859354782702987</x:v>
+      </x:c>
+      <x:c r="I21" s="52" t="n">
+        <x:v>-0.0161357202668575</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B22" s="52" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C22" s="52" t="n">
+        <x:v>1.121446863275139</x:v>
+      </x:c>
+      <x:c r="D22" s="52" t="n">
+        <x:v>1.0827941178711056</x:v>
+      </x:c>
+      <x:c r="E22" s="52" t="n">
+        <x:v>0.03865274540403352</x:v>
+      </x:c>
+      <x:c r="F22" s="52" t="n">
+        <x:v>1.1442970741476983</x:v>
+      </x:c>
+      <x:c r="G22" s="52" t="n">
+        <x:v>-0.02285021087255923</x:v>
+      </x:c>
+      <x:c r="H22" s="52" t="n">
+        <x:v>1.1368315468394217</x:v>
+      </x:c>
+      <x:c r="I22" s="52" t="n">
+        <x:v>-0.015384683564282575</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="52" t="str">
+        <x:v>Karaganda</x:v>
+      </x:c>
+      <x:c r="B23" s="52" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C23" s="52" t="n">
+        <x:v>1.2753481624898797</x:v>
+      </x:c>
+      <x:c r="D23" s="52" t="n">
+        <x:v>1.090062095136393</x:v>
+      </x:c>
+      <x:c r="E23" s="52" t="n">
+        <x:v>0.18528606735348663</x:v>
+      </x:c>
+      <x:c r="F23" s="52" t="n">
+        <x:v>1.1622706558343956</x:v>
+      </x:c>
+      <x:c r="G23" s="52" t="n">
+        <x:v>0.1130775066554841</x:v>
+      </x:c>
+      <x:c r="H23" s="52" t="n">
+        <x:v>1.1767503172945366</x:v>
+      </x:c>
+      <x:c r="I23" s="52" t="n">
+        <x:v>0.09859784519534309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B24" s="52" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C24" s="52" t="n">
+        <x:v>1.0969896438602886</x:v>
+      </x:c>
+      <x:c r="D24" s="52" t="n">
+        <x:v>1.015336777523019</x:v>
+      </x:c>
+      <x:c r="E24" s="52" t="n">
+        <x:v>0.08165286633726954</x:v>
+      </x:c>
+      <x:c r="F24" s="52" t="n">
+        <x:v>1.1582583997979914</x:v>
+      </x:c>
+      <x:c r="G24" s="52" t="n">
+        <x:v>-0.06126875593770276</x:v>
+      </x:c>
+      <x:c r="H24" s="52" t="n">
+        <x:v>1.1390217067653094</x:v>
+      </x:c>
+      <x:c r="I24" s="52" t="n">
+        <x:v>-0.04203206290502082</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B25" s="52" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C25" s="52" t="n">
+        <x:v>1.083291954810638</x:v>
+      </x:c>
+      <x:c r="D25" s="52" t="n">
+        <x:v>1.0226047547883066</x:v>
+      </x:c>
+      <x:c r="E25" s="52" t="n">
+        <x:v>0.0606872000223313</x:v>
+      </x:c>
+      <x:c r="F25" s="52" t="n">
+        <x:v>0.9775060430975404</x:v>
+      </x:c>
+      <x:c r="G25" s="52" t="n">
+        <x:v>0.10578591171309748</x:v>
+      </x:c>
+      <x:c r="H25" s="52" t="n">
+        <x:v>1.0134606895001628</x:v>
+      </x:c>
+      <x:c r="I25" s="52" t="n">
+        <x:v>0.06983126531047512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B26" s="52" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C26" s="52" t="n">
+        <x:v>1.012812316054036</x:v>
+      </x:c>
+      <x:c r="D26" s="52" t="n">
+        <x:v>1.0298727320535943</x:v>
+      </x:c>
+      <x:c r="E26" s="52" t="n">
+        <x:v>-0.01706041599955821</x:v>
+      </x:c>
+      <x:c r="F26" s="52" t="n">
+        <x:v>0.9661577019835174</x:v>
+      </x:c>
+      <x:c r="G26" s="52" t="n">
+        <x:v>0.04665461407051874</x:v>
+      </x:c>
+      <x:c r="H26" s="52" t="n">
+        <x:v>0.9989877340038589</x:v>
+      </x:c>
+      <x:c r="I26" s="52" t="n">
+        <x:v>0.013824582050177225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B27" s="52" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C27" s="52" t="n">
+        <x:v>1.0025049341624674</x:v>
+      </x:c>
+      <x:c r="D27" s="52" t="n">
+        <x:v>1.0371407093188818</x:v>
+      </x:c>
+      <x:c r="E27" s="52" t="n">
+        <x:v>-0.03463577515641436</x:v>
+      </x:c>
+      <x:c r="F27" s="52" t="n">
+        <x:v>0.9711975748769418</x:v>
+      </x:c>
+      <x:c r="G27" s="52" t="n">
+        <x:v>0.03130735928552564</x:v>
+      </x:c>
+      <x:c r="H27" s="52" t="n">
+        <x:v>0.9818010424269905</x:v>
+      </x:c>
+      <x:c r="I27" s="52" t="n">
+        <x:v>0.02070389173547693</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B28" s="52" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C28" s="52" t="n">
+        <x:v>0.97553166012387</x:v>
+      </x:c>
+      <x:c r="D28" s="52" t="n">
+        <x:v>1.0444086865841693</x:v>
+      </x:c>
+      <x:c r="E28" s="52" t="n">
+        <x:v>-0.06887702646029925</x:v>
+      </x:c>
+      <x:c r="F28" s="52" t="n">
+        <x:v>0.9925508513479621</x:v>
+      </x:c>
+      <x:c r="G28" s="52" t="n">
+        <x:v>-0.017019191224092012</x:v>
+      </x:c>
+      <x:c r="H28" s="52" t="n">
+        <x:v>1.0085637961583154</x:v>
+      </x:c>
+      <x:c r="I28" s="52" t="n">
+        <x:v>-0.033032136034445325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B29" s="52" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C29" s="52" t="n">
+        <x:v>0.9692931924059508</x:v>
+      </x:c>
+      <x:c r="D29" s="52" t="n">
+        <x:v>1.0516766638494568</x:v>
+      </x:c>
+      <x:c r="E29" s="52" t="n">
+        <x:v>-0.082383471443506</x:v>
+      </x:c>
+      <x:c r="F29" s="52" t="n">
+        <x:v>1.0305987221252608</x:v>
+      </x:c>
+      <x:c r="G29" s="52" t="n">
+        <x:v>-0.061305529719310026</x:v>
+      </x:c>
+      <x:c r="H29" s="52" t="n">
+        <x:v>1.0256693790291935</x:v>
+      </x:c>
+      <x:c r="I29" s="52" t="n">
+        <x:v>-0.05637618662324273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B30" s="52" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C30" s="52" t="n">
+        <x:v>0.9577101612387616</x:v>
+      </x:c>
+      <x:c r="D30" s="52" t="n">
+        <x:v>1.0589446411147445</x:v>
+      </x:c>
+      <x:c r="E30" s="52" t="n">
+        <x:v>-0.10123447987598289</x:v>
+      </x:c>
+      <x:c r="F30" s="52" t="n">
+        <x:v>1.0523183858754968</x:v>
+      </x:c>
+      <x:c r="G30" s="52" t="n">
+        <x:v>-0.09460822463673513</x:v>
+      </x:c>
+      <x:c r="H30" s="52" t="n">
+        <x:v>1.0399508040095586</x:v>
+      </x:c>
+      <x:c r="I30" s="52" t="n">
+        <x:v>-0.08224064277079701</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B31" s="52" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C31" s="52" t="n">
+        <x:v>0.9717110858523637</x:v>
+      </x:c>
+      <x:c r="D31" s="52" t="n">
+        <x:v>1.066212618380032</x:v>
+      </x:c>
+      <x:c r="E31" s="52" t="n">
+        <x:v>-0.09450153252766835</x:v>
+      </x:c>
+      <x:c r="F31" s="52" t="n">
+        <x:v>1.0446783791217529</x:v>
+      </x:c>
+      <x:c r="G31" s="52" t="n">
+        <x:v>-0.07296729326938922</x:v>
+      </x:c>
+      <x:c r="H31" s="52" t="n">
+        <x:v>1.0437992679407653</x:v>
+      </x:c>
+      <x:c r="I31" s="52" t="n">
+        <x:v>-0.07208818208840162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B32" s="52" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C32" s="52" t="n">
+        <x:v>0.9764503159103964</x:v>
+      </x:c>
+      <x:c r="D32" s="52" t="n">
+        <x:v>1.0734805956453195</x:v>
+      </x:c>
+      <x:c r="E32" s="52" t="n">
+        <x:v>-0.09703027973492306</x:v>
+      </x:c>
+      <x:c r="F32" s="52" t="n">
+        <x:v>1.0584808192548814</x:v>
+      </x:c>
+      <x:c r="G32" s="52" t="n">
+        <x:v>-0.08203050334448492</x:v>
+      </x:c>
+      <x:c r="H32" s="52" t="n">
+        <x:v>1.0380757556172477</x:v>
+      </x:c>
+      <x:c r="I32" s="52" t="n">
+        <x:v>-0.061625439706851304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B33" s="52" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C33" s="52" t="n">
+        <x:v>1.1551925165753971</x:v>
+      </x:c>
+      <x:c r="D33" s="52" t="n">
+        <x:v>1.0807485729106072</x:v>
+      </x:c>
+      <x:c r="E33" s="52" t="n">
+        <x:v>0.0744439436647899</x:v>
+      </x:c>
+      <x:c r="F33" s="52" t="n">
+        <x:v>1.150285540911481</x:v>
+      </x:c>
+      <x:c r="G33" s="52" t="n">
+        <x:v>0.00490697566391618</x:v>
+      </x:c>
+      <x:c r="H33" s="52" t="n">
+        <x:v>1.1355715309831567</x:v>
+      </x:c>
+      <x:c r="I33" s="52" t="n">
+        <x:v>0.01962098559224046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="52" t="str">
+        <x:v>Pavlodar</x:v>
+      </x:c>
+      <x:c r="B34" s="52" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C34" s="52" t="n">
+        <x:v>1.3669555213498588</x:v>
+      </x:c>
+      <x:c r="D34" s="52" t="n">
+        <x:v>1.0880165501758947</x:v>
+      </x:c>
+      <x:c r="E34" s="52" t="n">
+        <x:v>0.27893897117396405</x:v>
+      </x:c>
+      <x:c r="F34" s="52" t="n">
+        <x:v>1.166410883951222</x:v>
+      </x:c>
+      <x:c r="G34" s="52" t="n">
+        <x:v>0.20054463739863682</x:v>
+      </x:c>
+      <x:c r="H34" s="52" t="n">
+        <x:v>1.143541595909496</x:v>
+      </x:c>
+      <x:c r="I34" s="52" t="n">
+        <x:v>0.22341392544036287</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" customHeight="1">
+      <x:c r="A1" s="46" t="str">
         <x:v>Indicator</x:v>
       </x:c>
-      <x:c r="B1" s="44" t="str">
+      <x:c r="B1" s="47" t="str">
         <x:v>Exposed_mean_of_region_means</x:v>
       </x:c>
-      <x:c r="C1" s="44" t="str">
+      <x:c r="C1" s="47" t="str">
         <x:v>Comparison_mean_of_region_means</x:v>
       </x:c>
-      <x:c r="D1" s="44" t="str">
+      <x:c r="D1" s="47" t="str">
         <x:v>Difference_exposed_minus_comparison</x:v>
       </x:c>
-      <x:c r="E1" s="44" t="str">
+      <x:c r="E1" s="47" t="str">
         <x:v>Exposed_SD_across_regions</x:v>
       </x:c>
-      <x:c r="F1" s="44" t="str">
+      <x:c r="F1" s="47" t="str">
         <x:v>Comparison_SD_across_regions</x:v>
       </x:c>
-      <x:c r="G1" s="44" t="str">
+      <x:c r="G1" s="47" t="str">
+        <x:v>Exact_permutation_p_region_means</x:v>
+      </x:c>
+      <x:c r="H1" s="47" t="str">
+        <x:v>Permutation_allocations</x:v>
+      </x:c>
+      <x:c r="I1" s="47" t="str">
         <x:v>Welch_t_region_means</x:v>
       </x:c>
-      <x:c r="H1" s="44" t="str">
+      <x:c r="J1" s="47" t="str">
         <x:v>Welch_p_region_means</x:v>
       </x:c>
-      <x:c r="I1" s="44" t="str">
+      <x:c r="K1" s="46" t="str">
         <x:v>N_regions_exposed</x:v>
       </x:c>
-      <x:c r="J1" s="44" t="str">
+      <x:c r="L1" s="46" t="str">
         <x:v>N_regions_comparison</x:v>
       </x:c>
     </x:row>
@@ -5827,15 +10844,21 @@
         <x:v>0.07753063351123257</x:v>
       </x:c>
       <x:c r="G2" s="25" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H2" s="25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I2" s="25" t="n">
         <x:v>1.4826134040391095</x:v>
       </x:c>
-      <x:c r="H2" s="25" t="n">
+      <x:c r="J2" s="25" t="n">
         <x:v>0.269950464361062</x:v>
       </x:c>
-      <x:c r="I2" s="25" t="n">
+      <x:c r="K2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J2" s="25" t="n">
+      <x:c r="L2" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5859,15 +10882,21 @@
         <x:v>0.14690880020690153</x:v>
       </x:c>
       <x:c r="G3" s="25" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H3" s="25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I3" s="25" t="n">
         <x:v>-0.4285939227035905</x:v>
       </x:c>
-      <x:c r="H3" s="25" t="n">
+      <x:c r="J3" s="25" t="n">
         <x:v>0.6924560469237471</x:v>
       </x:c>
-      <x:c r="I3" s="25" t="n">
+      <x:c r="K3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J3" s="25" t="n">
+      <x:c r="L3" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5891,15 +10920,21 @@
         <x:v>0.27269120122308677</x:v>
       </x:c>
       <x:c r="G4" s="25" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H4" s="25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I4" s="25" t="n">
         <x:v>0.6963903131377864</x:v>
       </x:c>
-      <x:c r="H4" s="25" t="n">
+      <x:c r="J4" s="25" t="n">
         <x:v>0.5292485863440876</x:v>
       </x:c>
-      <x:c r="I4" s="25" t="n">
+      <x:c r="K4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J4" s="25" t="n">
+      <x:c r="L4" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5923,15 +10958,21 @@
         <x:v>0.8186925651247091</x:v>
       </x:c>
       <x:c r="G5" s="25" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H5" s="25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I5" s="25" t="n">
         <x:v>0.4404742008431818</x:v>
       </x:c>
-      <x:c r="H5" s="25" t="n">
+      <x:c r="J5" s="25" t="n">
         <x:v>0.6867169778742611</x:v>
       </x:c>
-      <x:c r="I5" s="25" t="n">
+      <x:c r="K5" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J5" s="25" t="n">
+      <x:c r="L5" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5955,15 +10996,21 @@
         <x:v>0.07734431367038454</x:v>
       </x:c>
       <x:c r="G6" s="25" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H6" s="25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="n">
         <x:v>-0.6714024780755286</x:v>
       </x:c>
-      <x:c r="H6" s="25" t="n">
+      <x:c r="J6" s="25" t="n">
         <x:v>0.5412195046930761</x:v>
       </x:c>
-      <x:c r="I6" s="25" t="n">
+      <x:c r="K6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J6" s="25" t="n">
+      <x:c r="L6" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5987,15 +11034,21 @@
         <x:v>0.22863812616588078</x:v>
       </x:c>
       <x:c r="G7" s="25" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="H7" s="25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I7" s="25" t="n">
         <x:v>0.8360815928151607</x:v>
       </x:c>
-      <x:c r="H7" s="25" t="n">
+      <x:c r="J7" s="25" t="n">
         <x:v>0.48786498185618404</x:v>
       </x:c>
-      <x:c r="I7" s="25" t="n">
+      <x:c r="K7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J7" s="25" t="n">
+      <x:c r="L7" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8815,15 +13868,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="45" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="39" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="46" t="str">
         <x:v>Statistic</x:v>
       </x:c>
-      <x:c r="B1" s="44" t="str">
+      <x:c r="B1" s="47" t="str">
         <x:v>Value</x:v>
       </x:c>
     </x:row>
@@ -8872,7 +13925,7 @@
         <x:v>KMO Cancer_pct</x:v>
       </x:c>
       <x:c r="B7" s="25" t="n">
-        <x:v>0.5690553031519888</x:v>
+        <x:v>0.5690553031519886</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -8896,7 +13949,7 @@
         <x:v>KMO Disability_pct</x:v>
       </x:c>
       <x:c r="B10" s="25" t="n">
-        <x:v>0.21630485331339994</x:v>
+        <x:v>0.21630485331340002</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -8912,7 +13965,7 @@
         <x:v>PC1 eigenvalue</x:v>
       </x:c>
       <x:c r="B12" s="25" t="n">
-        <x:v>2.5189261933951226</x:v>
+        <x:v>2.5189261933951244</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -8920,7 +13973,7 @@
         <x:v>PC1 explained variance ratio</x:v>
       </x:c>
       <x:c r="B13" s="25" t="n">
-        <x:v>0.4917903520438096</x:v>
+        <x:v>0.4917903520438095</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -8928,7 +13981,7 @@
         <x:v>PC2 eigenvalue</x:v>
       </x:c>
       <x:c r="B14" s="25" t="n">
-        <x:v>1.3333536497765754</x:v>
+        <x:v>1.3333536497765759</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8936,7 +13989,7 @@
         <x:v>PC2 explained variance ratio</x:v>
       </x:c>
       <x:c r="B15" s="25" t="n">
-        <x:v>0.2603214268611409</x:v>
+        <x:v>0.26032142686114074</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8944,7 +13997,7 @@
         <x:v>PC3 eigenvalue</x:v>
       </x:c>
       <x:c r="B16" s="25" t="n">
-        <x:v>0.5994252993343571</x:v>
+        <x:v>0.5994252993343585</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -8952,7 +14005,7 @@
         <x:v>PC3 explained variance ratio</x:v>
       </x:c>
       <x:c r="B17" s="25" t="n">
-        <x:v>0.11703065367956494</x:v>
+        <x:v>0.11703065367956511</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8960,7 +14013,7 @@
         <x:v>PC4 eigenvalue</x:v>
       </x:c>
       <x:c r="B18" s="25" t="n">
-        <x:v>0.5184094070783021</x:v>
+        <x:v>0.5184094070783035</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8968,7 +14021,7 @@
         <x:v>PC4 explained variance ratio</x:v>
       </x:c>
       <x:c r="B19" s="25" t="n">
-        <x:v>0.10121326519147802</x:v>
+        <x:v>0.1012132651914782</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -8976,7 +14029,7 @@
         <x:v>PC5 eigenvalue</x:v>
       </x:c>
       <x:c r="B20" s="25" t="n">
-        <x:v>0.15183666992783776</x:v>
+        <x:v>0.15183666992783781</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -8984,7 +14037,7 @@
         <x:v>PC5 explained variance ratio</x:v>
       </x:c>
       <x:c r="B21" s="25" t="n">
-        <x:v>0.02964430222400642</x:v>
+        <x:v>0.029644302224006398</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -8992,7 +14045,7 @@
         <x:v>PC1+PC2 cumulative explained variance</x:v>
       </x:c>
       <x:c r="B22" s="25" t="n">
-        <x:v>0.7521117789049505</x:v>
+        <x:v>0.7521117789049503</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9009,14 +14062,14 @@
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="39" t="str">
+    <x:row r="1" ht="58" customHeight="1">
+      <x:c r="A1" s="46" t="str">
         <x:v>Indicator</x:v>
       </x:c>
-      <x:c r="B1" s="44" t="str">
+      <x:c r="B1" s="47" t="str">
         <x:v>PC1_component_coefficient</x:v>
       </x:c>
-      <x:c r="C1" s="44" t="str">
+      <x:c r="C1" s="47" t="str">
         <x:v>PC2_component_coefficient</x:v>
       </x:c>
     </x:row>
@@ -9025,10 +14078,10 @@
         <x:v>Cancer_pct</x:v>
       </x:c>
       <x:c r="B2" s="25" t="n">
-        <x:v>-0.4503944067666221</x:v>
+        <x:v>-0.450394406766622</x:v>
       </x:c>
       <x:c r="C2" s="25" t="n">
-        <x:v>-0.38908905070829397</x:v>
+        <x:v>-0.3890890507082943</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9036,10 +14089,10 @@
         <x:v>Infant_mortality_pct</x:v>
       </x:c>
       <x:c r="B3" s="25" t="n">
-        <x:v>0.5126874599861008</x:v>
+        <x:v>0.5126874599861007</x:v>
       </x:c>
       <x:c r="C3" s="25" t="n">
-        <x:v>-0.026725580009736384</x:v>
+        <x:v>-0.02672558000973635</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -9047,10 +14100,10 @@
         <x:v>Circulatory_pct</x:v>
       </x:c>
       <x:c r="B4" s="25" t="n">
-        <x:v>-0.46472139695336256</x:v>
+        <x:v>-0.46472139695336273</x:v>
       </x:c>
       <x:c r="C4" s="25" t="n">
-        <x:v>-0.19332395974607736</x:v>
+        <x:v>-0.19332395974607713</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -9058,10 +14111,10 @@
         <x:v>Disability_pct</x:v>
       </x:c>
       <x:c r="B5" s="25" t="n">
-        <x:v>-0.08094676494027152</x:v>
+        <x:v>-0.08094676494027159</x:v>
       </x:c>
       <x:c r="C5" s="25" t="n">
-        <x:v>0.8381376995473874</x:v>
+        <x:v>0.8381376995473877</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -9069,10 +14122,10 @@
         <x:v>Unemployment_pct</x:v>
       </x:c>
       <x:c r="B6" s="25" t="n">
-        <x:v>0.5583709261644654</x:v>
+        <x:v>0.5583709261644655</x:v>
       </x:c>
       <x:c r="C6" s="25" t="n">
-        <x:v>-0.3287042700933053</x:v>
+        <x:v>-0.32870427009330516</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9096,35 +14149,35 @@
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="39" t="str">
+    <x:row r="1" ht="44" customHeight="1">
+      <x:c r="A1" s="46" t="str">
         <x:v>Region</x:v>
       </x:c>
-      <x:c r="B1" s="44" t="str">
+      <x:c r="B1" s="47" t="str">
         <x:v>Year</x:v>
       </x:c>
-      <x:c r="C1" s="44" t="str">
+      <x:c r="C1" s="47" t="str">
         <x:v>Mortality_pct</x:v>
       </x:c>
-      <x:c r="D1" s="44" t="str">
+      <x:c r="D1" s="47" t="str">
         <x:v>Z_Cancer_pct</x:v>
       </x:c>
-      <x:c r="E1" s="44" t="str">
+      <x:c r="E1" s="47" t="str">
         <x:v>Z_Infant_mortality_pct</x:v>
       </x:c>
-      <x:c r="F1" s="44" t="str">
+      <x:c r="F1" s="47" t="str">
         <x:v>Z_Circulatory_pct</x:v>
       </x:c>
-      <x:c r="G1" s="44" t="str">
+      <x:c r="G1" s="47" t="str">
         <x:v>Z_Disability_pct</x:v>
       </x:c>
-      <x:c r="H1" s="44" t="str">
+      <x:c r="H1" s="47" t="str">
         <x:v>Z_Unemployment_pct</x:v>
       </x:c>
-      <x:c r="I1" s="44" t="str">
+      <x:c r="I1" s="47" t="str">
         <x:v>PC1</x:v>
       </x:c>
-      <x:c r="J1" s="44" t="str">
+      <x:c r="J1" s="47" t="str">
         <x:v>PC2</x:v>
       </x:c>
     </x:row>
@@ -9154,10 +14207,10 @@
         <x:v>1.2901560704508215</x:v>
       </x:c>
       <x:c r="I2" s="25" t="n">
-        <x:v>3.291961740199841</x:v>
+        <x:v>3.29196174019984</x:v>
       </x:c>
       <x:c r="J2" s="25" t="n">
-        <x:v>-0.5836879305906996</x:v>
+        <x:v>-0.583687930590699</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9189,7 +14242,7 @@
         <x:v>2.9382967840345815</x:v>
       </x:c>
       <x:c r="J3" s="25" t="n">
-        <x:v>-0.5814777832241235</x:v>
+        <x:v>-0.5814777832241228</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -9221,7 +14274,7 @@
         <x:v>1.734880302455184</x:v>
       </x:c>
       <x:c r="J4" s="25" t="n">
-        <x:v>-0.41127619336858107</x:v>
+        <x:v>-0.41127619336858023</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -9250,10 +14303,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I5" s="25" t="n">
-        <x:v>0.34003340155086226</x:v>
+        <x:v>0.34003340155086237</x:v>
       </x:c>
       <x:c r="J5" s="25" t="n">
-        <x:v>-0.23670389652900348</x:v>
+        <x:v>-0.2367038965290033</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -9282,10 +14335,10 @@
         <x:v>0.5809683055494789</x:v>
       </x:c>
       <x:c r="I6" s="25" t="n">
-        <x:v>0.33389495871837344</x:v>
+        <x:v>0.33389495871837355</x:v>
       </x:c>
       <x:c r="J6" s="25" t="n">
-        <x:v>-0.5405427894343937</x:v>
+        <x:v>-0.5405427894343935</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -9314,10 +14367,10 @@
         <x:v>0.2263744230988092</x:v>
       </x:c>
       <x:c r="I7" s="25" t="n">
-        <x:v>-0.03942831578131832</x:v>
+        <x:v>-0.03942831578131827</x:v>
       </x:c>
       <x:c r="J7" s="25" t="n">
-        <x:v>-0.43624805245553494</x:v>
+        <x:v>-0.43624805245553455</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -9346,10 +14399,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I8" s="25" t="n">
-        <x:v>-0.9906942221820881</x:v>
+        <x:v>-0.9906942221820878</x:v>
       </x:c>
       <x:c r="J8" s="25" t="n">
-        <x:v>-0.5193384945358079</x:v>
+        <x:v>-0.5193384945358077</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -9381,7 +14434,7 @@
         <x:v>-0.6579792339404674</x:v>
       </x:c>
       <x:c r="J9" s="25" t="n">
-        <x:v>-0.2264849803514491</x:v>
+        <x:v>-0.22648498035144868</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -9410,10 +14463,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I10" s="25" t="n">
-        <x:v>-0.535861053830342</x:v>
+        <x:v>-0.5358610538303419</x:v>
       </x:c>
       <x:c r="J10" s="25" t="n">
-        <x:v>-0.4164637510037572</x:v>
+        <x:v>-0.41646375100375677</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -9442,10 +14495,10 @@
         <x:v>0.2263744230988092</x:v>
       </x:c>
       <x:c r="I11" s="25" t="n">
-        <x:v>0.20374906712215926</x:v>
+        <x:v>0.203749067122159</x:v>
       </x:c>
       <x:c r="J11" s="25" t="n">
-        <x:v>-0.043942554520308805</x:v>
+        <x:v>-0.0439425545203084</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -9474,10 +14527,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I12" s="25" t="n">
-        <x:v>-0.7236078884620494</x:v>
+        <x:v>-0.7236078884620493</x:v>
       </x:c>
       <x:c r="J12" s="25" t="n">
-        <x:v>-0.4560089160091204</x:v>
+        <x:v>-0.45600891600912014</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -9506,10 +14559,10 @@
         <x:v>0.003334871037337317</x:v>
       </x:c>
       <x:c r="I13" s="25" t="n">
-        <x:v>-1.4044137167933475</x:v>
+        <x:v>-1.4044137167933477</x:v>
       </x:c>
       <x:c r="J13" s="25" t="n">
-        <x:v>-0.7928748500447295</x:v>
+        <x:v>-0.792874850044729</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -9538,10 +14591,10 @@
         <x:v>-0.514726791223095</x:v>
       </x:c>
       <x:c r="I14" s="25" t="n">
-        <x:v>-1.9095019466053922</x:v>
+        <x:v>-1.9095019466053917</x:v>
       </x:c>
       <x:c r="J14" s="25" t="n">
-        <x:v>-0.8824142316485832</x:v>
+        <x:v>-0.8824142316485829</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -9570,10 +14623,10 @@
         <x:v>-0.5161451667528975</x:v>
       </x:c>
       <x:c r="I15" s="25" t="n">
-        <x:v>-1.9900981017510866</x:v>
+        <x:v>-1.9900981017510861</x:v>
       </x:c>
       <x:c r="J15" s="25" t="n">
-        <x:v>-0.8059593491854541</x:v>
+        <x:v>-0.8059593491854538</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -9602,10 +14655,10 @@
         <x:v>1.6447499529014913</x:v>
       </x:c>
       <x:c r="I16" s="25" t="n">
-        <x:v>2.8361151455954383</x:v>
+        <x:v>2.836115145595438</x:v>
       </x:c>
       <x:c r="J16" s="25" t="n">
-        <x:v>0.4390876256771303</x:v>
+        <x:v>0.43908762567713033</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -9634,7 +14687,7 @@
         <x:v>0.9355621880001487</x:v>
       </x:c>
       <x:c r="I17" s="25" t="n">
-        <x:v>2.2539090101156662</x:v>
+        <x:v>2.2539090101156654</x:v>
       </x:c>
       <x:c r="J17" s="25" t="n">
         <x:v>1.0984602089747446</x:v>
@@ -9669,7 +14722,7 @@
         <x:v>1.289946961924706</x:v>
       </x:c>
       <x:c r="J18" s="25" t="n">
-        <x:v>1.337566361818978</x:v>
+        <x:v>1.3375663618189777</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -9698,10 +14751,10 @@
         <x:v>0.2263744230988092</x:v>
       </x:c>
       <x:c r="I19" s="25" t="n">
-        <x:v>1.320784031154338</x:v>
+        <x:v>1.3207840311543377</x:v>
       </x:c>
       <x:c r="J19" s="25" t="n">
-        <x:v>1.4031908090756315</x:v>
+        <x:v>1.403190809075631</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -9733,7 +14786,7 @@
         <x:v>1.8738682861209306</x:v>
       </x:c>
       <x:c r="J20" s="25" t="n">
-        <x:v>0.7989711670900893</x:v>
+        <x:v>0.798971167090089</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -9762,10 +14815,10 @@
         <x:v>0.5809683055494789</x:v>
       </x:c>
       <x:c r="I21" s="25" t="n">
-        <x:v>1.054663971894671</x:v>
+        <x:v>1.0546639718946709</x:v>
       </x:c>
       <x:c r="J21" s="25" t="n">
-        <x:v>1.2358596497396015</x:v>
+        <x:v>1.235859649739601</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -9794,10 +14847,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I22" s="25" t="n">
-        <x:v>0.36623567139604124</x:v>
+        <x:v>0.366235671396041</x:v>
       </x:c>
       <x:c r="J22" s="25" t="n">
-        <x:v>1.5749518328182783</x:v>
+        <x:v>1.574951832818278</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -9826,7 +14879,7 @@
         <x:v>-0.8374072242532062</x:v>
       </x:c>
       <x:c r="I23" s="25" t="n">
-        <x:v>-0.6054432215398208</x:v>
+        <x:v>-0.605443221539821</x:v>
       </x:c>
       <x:c r="J23" s="25" t="n">
         <x:v>1.7773798157377794</x:v>
@@ -9858,10 +14911,10 @@
         <x:v>-1.5465949891545456</x:v>
       </x:c>
       <x:c r="I24" s="25" t="n">
-        <x:v>-0.9278933581901242</x:v>
+        <x:v>-0.9278933581901245</x:v>
       </x:c>
       <x:c r="J24" s="25" t="n">
-        <x:v>2.080391820811024</x:v>
+        <x:v>2.0803918208110233</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -9890,10 +14943,10 @@
         <x:v>-0.8374072242532062</x:v>
       </x:c>
       <x:c r="I25" s="25" t="n">
-        <x:v>0.19553900942827854</x:v>
+        <x:v>0.19553900942827787</x:v>
       </x:c>
       <x:c r="J25" s="25" t="n">
-        <x:v>2.480531563041965</x:v>
+        <x:v>2.4805315630419646</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -9922,10 +14975,10 @@
         <x:v>-1.192001106703876</x:v>
       </x:c>
       <x:c r="I26" s="25" t="n">
-        <x:v>-0.04737267764001473</x:v>
+        <x:v>-0.047372677640015244</x:v>
       </x:c>
       <x:c r="J26" s="25" t="n">
-        <x:v>2.340565363144942</x:v>
+        <x:v>2.340565363144941</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -9954,10 +15007,10 @@
         <x:v>-1.5465949891545456</x:v>
       </x:c>
       <x:c r="I27" s="25" t="n">
-        <x:v>-2.2856705657827123</x:v>
+        <x:v>-2.2856705657827114</x:v>
       </x:c>
       <x:c r="J27" s="25" t="n">
-        <x:v>1.0220490120079946</x:v>
+        <x:v>1.0220490120079937</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -9986,10 +15039,10 @@
         <x:v>-2.6103766365065613</x:v>
       </x:c>
       <x:c r="I28" s="25" t="n">
-        <x:v>-3.007505313096267</x:v>
+        <x:v>-3.007505313096266</x:v>
       </x:c>
       <x:c r="J28" s="25" t="n">
-        <x:v>1.7667107657194756</x:v>
+        <x:v>1.766710765719475</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -10021,7 +15074,7 @@
         <x:v>-3.317717183536329</x:v>
       </x:c>
       <x:c r="J29" s="25" t="n">
-        <x:v>1.5460850360892773</x:v>
+        <x:v>1.5460850360892764</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -10053,7 +15106,7 @@
         <x:v>3.164060943635321</x:v>
       </x:c>
       <x:c r="J30" s="25" t="n">
-        <x:v>-1.0458749003129946</x:v>
+        <x:v>-1.0458749003129943</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -10082,10 +15135,10 @@
         <x:v>1.2901560704508215</x:v>
       </x:c>
       <x:c r="I31" s="25" t="n">
-        <x:v>1.382151631501388</x:v>
+        <x:v>1.3821516315013884</x:v>
       </x:c>
       <x:c r="J31" s="25" t="n">
-        <x:v>-0.8351403568941916</x:v>
+        <x:v>-0.8351403568941919</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -10117,7 +15170,7 @@
         <x:v>0.920231612995435</x:v>
       </x:c>
       <x:c r="J32" s="25" t="n">
-        <x:v>-0.4863552890690995</x:v>
+        <x:v>-0.4863552890690998</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -10146,10 +15199,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I33" s="25" t="n">
-        <x:v>0.4223496435344996</x:v>
+        <x:v>0.4223496435344999</x:v>
       </x:c>
       <x:c r="J33" s="25" t="n">
-        <x:v>-0.6284415037376611</x:v>
+        <x:v>-0.6284415037376615</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -10178,10 +15231,10 @@
         <x:v>0.2263744230988092</x:v>
       </x:c>
       <x:c r="I34" s="25" t="n">
-        <x:v>0.20498686953501496</x:v>
+        <x:v>0.20498686953501508</x:v>
       </x:c>
       <x:c r="J34" s="25" t="n">
-        <x:v>-0.8001697517022139</x:v>
+        <x:v>-0.800169751702214</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -10210,10 +15263,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I35" s="25" t="n">
-        <x:v>-0.12080333123714014</x:v>
+        <x:v>-0.1208033312371398</x:v>
       </x:c>
       <x:c r="J35" s="25" t="n">
-        <x:v>-1.0235800445414631</x:v>
+        <x:v>-1.0235800445414633</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -10242,10 +15295,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I36" s="25" t="n">
-        <x:v>-0.48114149102690623</x:v>
+        <x:v>-0.48114149102690557</x:v>
       </x:c>
       <x:c r="J36" s="25" t="n">
-        <x:v>-1.2716673173980069</x:v>
+        <x:v>-1.2716673173980073</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -10274,10 +15327,10 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I37" s="25" t="n">
-        <x:v>-0.7549371106048456</x:v>
+        <x:v>-0.7549371106048455</x:v>
       </x:c>
       <x:c r="J37" s="25" t="n">
-        <x:v>-0.9602204447627738</x:v>
+        <x:v>-0.9602204447627737</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -10306,10 +15359,10 @@
         <x:v>-0.4828133418025334</x:v>
       </x:c>
       <x:c r="I38" s="25" t="n">
-        <x:v>-1.4068747487901403</x:v>
+        <x:v>-1.4068747487901399</x:v>
       </x:c>
       <x:c r="J38" s="25" t="n">
-        <x:v>-1.347204764246103</x:v>
+        <x:v>-1.3472047642461027</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -10341,7 +15394,7 @@
         <x:v>-0.6397005803435311</x:v>
       </x:c>
       <x:c r="J39" s="25" t="n">
-        <x:v>-0.7152269942214007</x:v>
+        <x:v>-0.7152269942214005</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -10373,7 +15426,7 @@
         <x:v>-1.3280244671386083</x:v>
       </x:c>
       <x:c r="J40" s="25" t="n">
-        <x:v>-1.446272867393398</x:v>
+        <x:v>-1.4462728673933978</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -10402,7 +15455,7 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I41" s="25" t="n">
-        <x:v>-0.9506876150379912</x:v>
+        <x:v>-0.9506876150379906</x:v>
       </x:c>
       <x:c r="J41" s="25" t="n">
         <x:v>-1.3501837938488401</x:v>
@@ -10434,7 +15487,7 @@
         <x:v>-0.12821945935186366</x:v>
       </x:c>
       <x:c r="I42" s="25" t="n">
-        <x:v>-0.8983466997978704</x:v>
+        <x:v>-0.8983466997978703</x:v>
       </x:c>
       <x:c r="J42" s="25" t="n">
         <x:v>-1.1568030275034618</x:v>
@@ -10466,10 +15519,10 @@
         <x:v>-0.4828133418025334</x:v>
       </x:c>
       <x:c r="I43" s="25" t="n">
-        <x:v>-1.1039561998043355</x:v>
+        <x:v>-1.103956199804335</x:v>
       </x:c>
       <x:c r="J43" s="25" t="n">
-        <x:v>-0.9012362032137559</x:v>
+        <x:v>-0.9012362032137556</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
